--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -38248,6 +38248,408 @@
         </is>
       </c>
     </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M192" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="O192" t="n">
+        <v>0</v>
+      </c>
+      <c r="P192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="n">
+        <v>0</v>
+      </c>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U192" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO192" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP192" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ192" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS192" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT192" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU192" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV192" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW192" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX192" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY192" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA192" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB192" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC192" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" t="n">
+        <v>0</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38281,7 +38683,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -38364,7 +38766,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -38374,7 +38776,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="11">
@@ -38394,7 +38796,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -927,9 +927,6 @@
       <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="S3" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -1320,9 +1317,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1716,9 +1710,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1878,9 +1869,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -2127,7 +2115,7 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN9" t="b">
@@ -2274,9 +2262,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2919,7 +2904,7 @@
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN13" t="b">
@@ -3066,9 +3051,6 @@
       <c r="O14" t="n">
         <v>1</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -3465,9 +3447,6 @@
       <c r="P16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -3717,7 +3696,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN17" t="b">
@@ -4119,7 +4098,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN19" t="b">
@@ -4521,7 +4500,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN21" t="b">
@@ -4923,7 +4902,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN23" t="b">
@@ -5232,9 +5211,6 @@
       <c r="O25" t="n">
         <v>6</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -5625,9 +5601,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -6021,9 +5994,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6438,7 +6408,7 @@
       </c>
       <c r="AM31" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN31" t="b">
@@ -6585,9 +6555,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6834,7 +6801,7 @@
       </c>
       <c r="AM33" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN33" t="b">
@@ -6981,9 +6948,6 @@
       <c r="O34" t="n">
         <v>0</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0</v>
       </c>
@@ -7626,7 +7590,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN37" t="b">
@@ -7773,9 +7737,6 @@
       <c r="O38" t="n">
         <v>0</v>
       </c>
-      <c r="Q38" t="n">
-        <v>0</v>
-      </c>
       <c r="R38" t="n">
         <v>0</v>
       </c>
@@ -8424,7 +8385,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN41" t="b">
@@ -8826,7 +8787,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN43" t="b">
@@ -9228,7 +9189,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN45" t="b">
@@ -9537,9 +9498,6 @@
       <c r="O47" t="n">
         <v>6</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="S47" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -9930,9 +9888,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -10326,9 +10281,6 @@
       <c r="O51" t="n">
         <v>1</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -10575,7 +10527,7 @@
       </c>
       <c r="AM52" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN52" t="b">
@@ -10977,7 +10929,7 @@
       </c>
       <c r="AM54" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN54" t="b">
@@ -11124,9 +11076,6 @@
       <c r="O55" t="n">
         <v>1</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -11373,7 +11322,7 @@
       </c>
       <c r="AM56" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN56" t="b">
@@ -11520,9 +11469,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -12165,7 +12111,7 @@
       </c>
       <c r="AM60" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN60" t="b">
@@ -12312,9 +12258,6 @@
       <c r="O61" t="n">
         <v>1</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -12963,7 +12906,7 @@
       </c>
       <c r="AM64" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN64" t="b">
@@ -13113,9 +13056,6 @@
       <c r="P65" t="n">
         <v>1</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -13767,7 +13707,7 @@
       </c>
       <c r="AM68" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN68" t="b">
@@ -13917,9 +13857,6 @@
       <c r="P69" t="n">
         <v>1</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -14571,7 +14508,7 @@
       </c>
       <c r="AM72" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN72" t="b">
@@ -14973,7 +14910,7 @@
       </c>
       <c r="AM74" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN74" t="b">
@@ -15120,9 +15057,6 @@
       <c r="O75" t="n">
         <v>6</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.02203687091711874</v>
       </c>
@@ -15282,9 +15216,6 @@
       <c r="O76" t="n">
         <v>5</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="S76" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -15675,9 +15606,6 @@
       <c r="O78" t="n">
         <v>1</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -16071,9 +15999,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -16320,7 +16245,7 @@
       </c>
       <c r="AM81" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN81" t="b">
@@ -16467,9 +16392,6 @@
       <c r="O82" t="n">
         <v>3</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.005813909771376137</v>
       </c>
@@ -16716,7 +16638,7 @@
       </c>
       <c r="AM83" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN83" t="b">
@@ -16863,9 +16785,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -17259,9 +17178,6 @@
       <c r="O86" t="n">
         <v>4</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.07565041865887316</v>
       </c>
@@ -17508,7 +17424,7 @@
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -17655,9 +17571,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -18054,9 +17967,6 @@
       <c r="P90" t="n">
         <v>1</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -18708,7 +18618,7 @@
       </c>
       <c r="AM93" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN93" t="b">
@@ -18858,9 +18768,6 @@
       <c r="P94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -19512,7 +19419,7 @@
       </c>
       <c r="AM97" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN97" t="b">
@@ -19662,9 +19569,6 @@
       <c r="P98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -20316,7 +20220,7 @@
       </c>
       <c r="AM101" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN101" t="b">
@@ -20718,7 +20622,7 @@
       </c>
       <c r="AM103" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN103" t="b">
@@ -20865,9 +20769,6 @@
       <c r="O104" t="n">
         <v>0</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0</v>
       </c>
@@ -21027,9 +20928,6 @@
       <c r="O105" t="n">
         <v>4</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="S105" t="inlineStr">
         <is>
           <t>missing_population</t>
@@ -21420,9 +21318,6 @@
       <c r="O107" t="n">
         <v>0</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0</v>
       </c>
@@ -21816,9 +21711,6 @@
       <c r="O109" t="n">
         <v>2</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.02710540560393419</v>
       </c>
@@ -22065,7 +21957,7 @@
       </c>
       <c r="AM110" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN110" t="b">
@@ -22212,9 +22104,6 @@
       <c r="O111" t="n">
         <v>1</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -22461,7 +22350,7 @@
       </c>
       <c r="AM112" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN112" t="b">
@@ -22608,9 +22497,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -23004,9 +22890,6 @@
       <c r="O115" t="n">
         <v>3</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.05673781399415487</v>
       </c>
@@ -23253,7 +23136,7 @@
       </c>
       <c r="AM116" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN116" t="b">
@@ -23400,9 +23283,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -23796,9 +23676,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -24199,7 +24076,7 @@
       </c>
       <c r="AM121" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN121" t="b">
@@ -24601,7 +24478,7 @@
       </c>
       <c r="AM123" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN123" t="b">
@@ -24751,9 +24628,6 @@
       <c r="P124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -25405,7 +25279,7 @@
       </c>
       <c r="AM127" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN127" t="b">
@@ -25555,9 +25429,6 @@
       <c r="P128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -26209,7 +26080,7 @@
       </c>
       <c r="AM131" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN131" t="b">
@@ -26611,7 +26482,7 @@
       </c>
       <c r="AM133" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN133" t="b">
@@ -26758,9 +26629,6 @@
       <c r="O134" t="n">
         <v>0</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0</v>
       </c>
@@ -27154,9 +27022,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.01778809170864137</v>
       </c>
@@ -27550,9 +27415,6 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.01355270280196709</v>
       </c>
@@ -27799,7 +27661,7 @@
       </c>
       <c r="AM139" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN139" t="b">
@@ -27946,9 +27808,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -28195,7 +28054,7 @@
       </c>
       <c r="AM141" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN141" t="b">
@@ -28342,9 +28201,6 @@
       <c r="O142" t="n">
         <v>0</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0</v>
       </c>
@@ -28738,9 +28594,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.01891260466471829</v>
       </c>
@@ -28987,7 +28840,7 @@
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -29134,9 +28987,6 @@
       <c r="O146" t="n">
         <v>0</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0</v>
       </c>
@@ -29533,9 +29383,6 @@
       <c r="P148" t="n">
         <v>1</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -29785,7 +29632,7 @@
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -29935,9 +29782,6 @@
       <c r="P150" t="n">
         <v>1</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -30337,9 +30181,6 @@
       <c r="P152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -30589,7 +30430,7 @@
       </c>
       <c r="AM153" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN153" t="b">
@@ -30739,9 +30580,6 @@
       <c r="P154" t="n">
         <v>1</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -31141,9 +30979,6 @@
       <c r="P156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -31393,7 +31228,7 @@
       </c>
       <c r="AM157" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN157" t="b">
@@ -31543,9 +31378,6 @@
       <c r="P158" t="n">
         <v>1</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -31945,9 +31777,6 @@
       <c r="P160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -32197,7 +32026,7 @@
       </c>
       <c r="AM161" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN161" t="b">
@@ -32344,9 +32173,6 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -32740,9 +32566,6 @@
       <c r="O164" t="n">
         <v>2</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -33136,9 +32959,6 @@
       <c r="O166" t="n">
         <v>1</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.001937969923792046</v>
       </c>
@@ -33385,7 +33205,7 @@
       </c>
       <c r="AM167" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN167" t="b">
@@ -33532,9 +33352,6 @@
       <c r="O168" t="n">
         <v>1</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.01768975825795506</v>
       </c>
@@ -33928,9 +33745,6 @@
       <c r="O170" t="n">
         <v>1</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.009344880428283346</v>
       </c>
@@ -34327,9 +34141,6 @@
       <c r="P172" t="n">
         <v>1</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.0008168084075657662</v>
       </c>
@@ -34579,7 +34390,7 @@
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34729,9 +34540,6 @@
       <c r="P174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -34981,7 +34789,7 @@
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -35131,9 +34939,6 @@
       <c r="P176" t="n">
         <v>2</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.0005730076265538771</v>
       </c>
@@ -35533,9 +35338,6 @@
       <c r="P178" t="n">
         <v>0</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0</v>
       </c>
@@ -35785,7 +35587,7 @@
       </c>
       <c r="AM179" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN179" t="b">
@@ -35935,9 +35737,6 @@
       <c r="P180" t="n">
         <v>0</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0</v>
       </c>
@@ -36187,7 +35986,7 @@
       </c>
       <c r="AM181" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN181" t="b">
@@ -36334,9 +36133,6 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -36730,9 +36526,6 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
-      <c r="Q184" t="n">
-        <v>0</v>
-      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -37126,9 +36919,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -37375,7 +37165,7 @@
       </c>
       <c r="AM187" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN187" t="b">
@@ -37522,9 +37312,6 @@
       <c r="O188" t="n">
         <v>0</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0</v>
       </c>
@@ -37921,9 +37708,6 @@
       <c r="P190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -38323,9 +38107,6 @@
       <c r="P192" t="n">
         <v>0</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0</v>
       </c>
@@ -38575,7 +38356,7 @@
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN193" t="b">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -26978,12 +26978,12 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -27017,22 +27017,19 @@
         </is>
       </c>
       <c r="N136" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O136" t="n">
-        <v>1</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0.01778809170864137</v>
+        <v>3</v>
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="U136" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_CA_ON_PHO_IDTO_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -27052,12 +27049,12 @@
       </c>
       <c r="AQ136" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS136" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_CA_ON_PHO_IDTO_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT136" t="n">
@@ -27065,47 +27062,47 @@
       </c>
       <c r="AU136" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA136" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB136" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC136" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27137,12 +27134,12 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
@@ -27176,29 +27173,29 @@
         </is>
       </c>
       <c r="N137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O137" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="U137" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_CA_ON_PHO_IDTO_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V137" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_CA_ON_PHO_IDTO_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W137" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CA_ON_PHO_IDTO</t>
         </is>
       </c>
       <c r="X137" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid Fever</t>
         </is>
       </c>
       <c r="Y137" t="inlineStr">
@@ -27208,7 +27205,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -27223,7 +27220,7 @@
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CA-ON:national</t>
         </is>
       </c>
       <c r="AD137" t="inlineStr">
@@ -27258,17 +27255,17 @@
       </c>
       <c r="AJ137" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>PHO_IDTO_2026_07</t>
         </is>
       </c>
       <c r="AK137" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>PHO IDTO current-year monthly preliminary paratyphoid fever notifications, separate from typhoid fever; confirmed cases only under the July 2026 technical notes.</t>
         </is>
       </c>
       <c r="AM137" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN137" t="b">
@@ -27286,12 +27283,12 @@
       </c>
       <c r="AQ137" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS137" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_CA_ON_PHO_IDTO_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT137" t="n">
@@ -27299,47 +27296,47 @@
       </c>
       <c r="AU137" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA137" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB137" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC137" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -27371,12 +27368,12 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
@@ -27416,7 +27413,7 @@
         <v>1</v>
       </c>
       <c r="R138" t="n">
-        <v>0.01355270280196709</v>
+        <v>0.01778809170864137</v>
       </c>
       <c r="S138" t="inlineStr">
         <is>
@@ -27425,7 +27422,7 @@
       </c>
       <c r="U138" t="inlineStr">
         <is>
-          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -27435,7 +27432,7 @@
       </c>
       <c r="AO138" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP138" t="inlineStr">
@@ -27445,12 +27442,12 @@
       </c>
       <c r="AQ138" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS138" t="inlineStr">
         <is>
-          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT138" t="n">
@@ -27458,47 +27455,47 @@
       </c>
       <c r="AU138" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV138" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA138" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB138" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC138" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27530,12 +27527,12 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>HK</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hong Kong, China</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -27576,22 +27573,22 @@
       </c>
       <c r="U139" t="inlineStr">
         <is>
-          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V139" t="inlineStr">
         <is>
-          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W139" t="inlineStr">
         <is>
-          <t>SRC_HK_CHP</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X139" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y139" t="inlineStr">
@@ -27601,7 +27598,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -27616,7 +27613,7 @@
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>country:HK:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD139" t="inlineStr">
@@ -27651,12 +27648,12 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>HK_CHP_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM139" t="inlineStr">
@@ -27669,7 +27666,7 @@
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP139" t="inlineStr">
@@ -27679,12 +27676,12 @@
       </c>
       <c r="AQ139" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS139" t="inlineStr">
         <is>
-          <t>SER_HK_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT139" t="n">
@@ -27692,47 +27689,47 @@
       </c>
       <c r="AU139" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV139" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>chp_notifiable</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA139" t="inlineStr">
         <is>
-          <t>Hong Kong, China CHP Notifiable Diseases</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB139" t="inlineStr">
         <is>
-          <t>https://www.chp.gov.hk/en/static/24012.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC139" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -27764,12 +27761,12 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
@@ -27809,7 +27806,7 @@
         <v>1</v>
       </c>
       <c r="R140" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S140" t="inlineStr">
         <is>
@@ -27818,7 +27815,7 @@
       </c>
       <c r="U140" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -27828,7 +27825,7 @@
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP140" t="inlineStr">
@@ -27838,12 +27835,12 @@
       </c>
       <c r="AQ140" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS140" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT140" t="n">
@@ -27851,47 +27848,47 @@
       </c>
       <c r="AU140" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV140" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA140" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB140" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC140" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -27923,12 +27920,12 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
@@ -27969,22 +27966,22 @@
       </c>
       <c r="U141" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V141" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W141" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_HK_CHP</t>
         </is>
       </c>
       <c r="X141" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y141" t="inlineStr">
@@ -28009,7 +28006,7 @@
       </c>
       <c r="AC141" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:HK:national</t>
         </is>
       </c>
       <c r="AD141" t="inlineStr">
@@ -28044,12 +28041,12 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>HK_CHP_current</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Hong Kong, China CHP paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM141" t="inlineStr">
@@ -28062,7 +28059,7 @@
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP141" t="inlineStr">
@@ -28072,12 +28069,12 @@
       </c>
       <c r="AQ141" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS141" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT141" t="n">
@@ -28085,47 +28082,47 @@
       </c>
       <c r="AU141" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA141" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB141" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC141" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -28157,12 +28154,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -28196,13 +28193,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O142" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R142" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -28211,7 +28208,7 @@
       </c>
       <c r="U142" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
@@ -28236,7 +28233,7 @@
       </c>
       <c r="AS142" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT142" t="n">
@@ -28249,42 +28246,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28316,12 +28313,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -28355,29 +28352,29 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U143" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V143" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W143" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X143" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y143" t="inlineStr">
@@ -28387,7 +28384,7 @@
       </c>
       <c r="Z143" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
@@ -28402,7 +28399,7 @@
       </c>
       <c r="AC143" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD143" t="inlineStr">
@@ -28437,17 +28434,17 @@
       </c>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM143" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN143" t="b">
@@ -28470,7 +28467,7 @@
       </c>
       <c r="AS143" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT143" t="n">
@@ -28483,42 +28480,42 @@
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -28550,12 +28547,12 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
@@ -28589,13 +28586,13 @@
         </is>
       </c>
       <c r="N144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R144" t="n">
-        <v>0.01891260466471829</v>
+        <v>0</v>
       </c>
       <c r="S144" t="inlineStr">
         <is>
@@ -28604,7 +28601,7 @@
       </c>
       <c r="U144" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
@@ -28629,7 +28626,7 @@
       </c>
       <c r="AS144" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT144" t="n">
@@ -28642,42 +28639,42 @@
       </c>
       <c r="AV144" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA144" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB144" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC144" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28709,12 +28706,12 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -28748,29 +28745,29 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U145" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V145" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W145" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X145" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y145" t="inlineStr">
@@ -28780,7 +28777,7 @@
       </c>
       <c r="Z145" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
@@ -28795,7 +28792,7 @@
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD145" t="inlineStr">
@@ -28830,17 +28827,17 @@
       </c>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science paratyphoid-only notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM145" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN145" t="b">
@@ -28863,7 +28860,7 @@
       </c>
       <c r="AS145" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT145" t="n">
@@ -28876,42 +28873,42 @@
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -28943,12 +28940,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -28982,13 +28979,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O146" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R146" t="n">
-        <v>0</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -28997,7 +28994,7 @@
       </c>
       <c r="U146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
@@ -29022,7 +29019,7 @@
       </c>
       <c r="AS146" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT146" t="n">
@@ -29035,42 +29032,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29102,12 +29099,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -29141,29 +29138,29 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W147" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X147" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y147" t="inlineStr">
@@ -29173,7 +29170,7 @@
       </c>
       <c r="Z147" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
@@ -29188,7 +29185,7 @@
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD147" t="inlineStr">
@@ -29223,17 +29220,17 @@
       </c>
       <c r="AJ147" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK147" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
+          <t>New Zealand PHF Science paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM147" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN147" t="b">
@@ -29256,7 +29253,7 @@
       </c>
       <c r="AS147" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT147" t="n">
@@ -29269,42 +29266,42 @@
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29336,12 +29333,12 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
@@ -29366,7 +29363,7 @@
       </c>
       <c r="L148" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M148" t="inlineStr">
@@ -29375,16 +29372,13 @@
         </is>
       </c>
       <c r="N148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O148" t="n">
-        <v>1</v>
-      </c>
-      <c r="P148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0</v>
       </c>
       <c r="S148" t="inlineStr">
         <is>
@@ -29393,17 +29387,17 @@
       </c>
       <c r="U148" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP148" t="inlineStr">
@@ -29413,12 +29407,12 @@
       </c>
       <c r="AQ148" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS148" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT148" t="n">
@@ -29426,47 +29420,47 @@
       </c>
       <c r="AU148" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA148" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB148" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC148" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29498,12 +29492,12 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -29528,7 +29522,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-06-07</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -29537,32 +29531,29 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O149" t="n">
-        <v>1</v>
-      </c>
-      <c r="P149" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="V149" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="W149" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X149" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y149" t="inlineStr">
@@ -29572,12 +29563,12 @@
       </c>
       <c r="Z149" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB149" t="inlineStr">
@@ -29587,7 +29578,7 @@
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD149" t="inlineStr">
@@ -29622,17 +29613,17 @@
       </c>
       <c r="AJ149" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK149" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
         </is>
       </c>
       <c r="AM149" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN149" t="b">
@@ -29640,7 +29631,7 @@
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
@@ -29650,12 +29641,12 @@
       </c>
       <c r="AQ149" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS149" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT149" t="n">
@@ -29663,47 +29654,47 @@
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -29735,12 +29726,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -29765,7 +29756,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -29783,7 +29774,7 @@
         <v>1</v>
       </c>
       <c r="R150" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
@@ -29792,7 +29783,7 @@
       </c>
       <c r="U150" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
@@ -29802,7 +29793,7 @@
       </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
@@ -29812,12 +29803,12 @@
       </c>
       <c r="AQ150" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS150" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT150" t="n">
@@ -29825,47 +29816,47 @@
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29897,12 +29888,12 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
@@ -29927,7 +29918,7 @@
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t>2026-06-13</t>
+          <t>2026-06-07</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
@@ -29946,22 +29937,22 @@
       </c>
       <c r="U151" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V151" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W151" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X151" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y151" t="inlineStr">
@@ -29986,7 +29977,7 @@
       </c>
       <c r="AC151" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD151" t="inlineStr">
@@ -30021,12 +30012,12 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM151" t="inlineStr">
@@ -30039,7 +30030,7 @@
       </c>
       <c r="AO151" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP151" t="inlineStr">
@@ -30049,12 +30040,12 @@
       </c>
       <c r="AQ151" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS151" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT151" t="n">
@@ -30062,47 +30053,47 @@
       </c>
       <c r="AU151" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV151" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA151" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB151" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC151" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30134,12 +30125,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -30164,7 +30155,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -30182,7 +30173,7 @@
         <v>1</v>
       </c>
       <c r="R152" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S152" t="inlineStr">
         <is>
@@ -30191,7 +30182,7 @@
       </c>
       <c r="U152" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
@@ -30201,7 +30192,7 @@
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
@@ -30211,12 +30202,12 @@
       </c>
       <c r="AQ152" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS152" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT152" t="n">
@@ -30224,47 +30215,47 @@
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30296,12 +30287,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -30326,7 +30317,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-06-14</t>
+          <t>2026-06-13</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -30345,22 +30336,22 @@
       </c>
       <c r="U153" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V153" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W153" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X153" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y153" t="inlineStr">
@@ -30385,7 +30376,7 @@
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD153" t="inlineStr">
@@ -30420,12 +30411,12 @@
       </c>
       <c r="AJ153" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK153" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM153" t="inlineStr">
@@ -30438,7 +30429,7 @@
       </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
@@ -30448,12 +30439,12 @@
       </c>
       <c r="AQ153" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS153" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT153" t="n">
@@ -30461,47 +30452,47 @@
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -30533,12 +30524,12 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -30563,7 +30554,7 @@
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
@@ -30581,7 +30572,7 @@
         <v>1</v>
       </c>
       <c r="R154" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S154" t="inlineStr">
         <is>
@@ -30590,7 +30581,7 @@
       </c>
       <c r="U154" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
@@ -30600,7 +30591,7 @@
       </c>
       <c r="AO154" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP154" t="inlineStr">
@@ -30610,12 +30601,12 @@
       </c>
       <c r="AQ154" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS154" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT154" t="n">
@@ -30623,47 +30614,47 @@
       </c>
       <c r="AU154" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV154" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA154" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB154" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC154" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30695,12 +30686,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -30725,7 +30716,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-06-20</t>
+          <t>2026-06-14</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -30744,22 +30735,22 @@
       </c>
       <c r="U155" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V155" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W155" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X155" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y155" t="inlineStr">
@@ -30784,7 +30775,7 @@
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD155" t="inlineStr">
@@ -30819,12 +30810,12 @@
       </c>
       <c r="AJ155" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK155" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM155" t="inlineStr">
@@ -30837,7 +30828,7 @@
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
@@ -30847,12 +30838,12 @@
       </c>
       <c r="AQ155" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS155" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT155" t="n">
@@ -30860,47 +30851,47 @@
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30932,12 +30923,12 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -30962,7 +30953,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -30971,16 +30962,16 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P156" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R156" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -30989,7 +30980,7 @@
       </c>
       <c r="U156" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
@@ -30999,7 +30990,7 @@
       </c>
       <c r="AO156" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP156" t="inlineStr">
@@ -31009,12 +31000,12 @@
       </c>
       <c r="AQ156" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS156" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT156" t="n">
@@ -31022,47 +31013,47 @@
       </c>
       <c r="AU156" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA156" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB156" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC156" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31094,12 +31085,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -31124,7 +31115,7 @@
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-06-20</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
@@ -31133,32 +31124,32 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P157" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V157" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W157" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X157" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y157" t="inlineStr">
@@ -31183,7 +31174,7 @@
       </c>
       <c r="AC157" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD157" t="inlineStr">
@@ -31218,12 +31209,12 @@
       </c>
       <c r="AJ157" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK157" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM157" t="inlineStr">
@@ -31236,7 +31227,7 @@
       </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
@@ -31246,12 +31237,12 @@
       </c>
       <c r="AQ157" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS157" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT157" t="n">
@@ -31259,47 +31250,47 @@
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31331,12 +31322,12 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -31361,7 +31352,7 @@
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
@@ -31370,16 +31361,16 @@
         </is>
       </c>
       <c r="N158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P158" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R158" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S158" t="inlineStr">
         <is>
@@ -31388,7 +31379,7 @@
       </c>
       <c r="U158" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
@@ -31398,7 +31389,7 @@
       </c>
       <c r="AO158" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP158" t="inlineStr">
@@ -31408,12 +31399,12 @@
       </c>
       <c r="AQ158" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS158" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT158" t="n">
@@ -31421,47 +31412,47 @@
       </c>
       <c r="AU158" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV158" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA158" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB158" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC158" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31493,12 +31484,12 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -31523,7 +31514,7 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-06-27</t>
+          <t>2026-06-21</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
@@ -31532,32 +31523,32 @@
         </is>
       </c>
       <c r="N159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P159" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V159" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W159" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X159" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y159" t="inlineStr">
@@ -31582,7 +31573,7 @@
       </c>
       <c r="AC159" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD159" t="inlineStr">
@@ -31617,12 +31608,12 @@
       </c>
       <c r="AJ159" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK159" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM159" t="inlineStr">
@@ -31635,7 +31626,7 @@
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
@@ -31645,12 +31636,12 @@
       </c>
       <c r="AQ159" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS159" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT159" t="n">
@@ -31658,47 +31649,47 @@
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -31730,12 +31721,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -31760,7 +31751,7 @@
       </c>
       <c r="L160" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M160" t="inlineStr">
@@ -31769,16 +31760,16 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R160" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
@@ -31787,7 +31778,7 @@
       </c>
       <c r="U160" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
@@ -31797,7 +31788,7 @@
       </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
@@ -31807,12 +31798,12 @@
       </c>
       <c r="AQ160" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS160" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT160" t="n">
@@ -31820,47 +31811,47 @@
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -31892,12 +31883,12 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -31922,7 +31913,7 @@
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>2026-06-28</t>
+          <t>2026-06-27</t>
         </is>
       </c>
       <c r="M161" t="inlineStr">
@@ -31931,32 +31922,32 @@
         </is>
       </c>
       <c r="N161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V161" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W161" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X161" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y161" t="inlineStr">
@@ -31981,7 +31972,7 @@
       </c>
       <c r="AC161" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD161" t="inlineStr">
@@ -32016,12 +32007,12 @@
       </c>
       <c r="AJ161" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK161" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM161" t="inlineStr">
@@ -32034,7 +32025,7 @@
       </c>
       <c r="AO161" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP161" t="inlineStr">
@@ -32044,12 +32035,12 @@
       </c>
       <c r="AQ161" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS161" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT161" t="n">
@@ -32057,47 +32048,47 @@
       </c>
       <c r="AU161" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA161" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB161" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC161" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -32129,12 +32120,12 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -32159,12 +32150,12 @@
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N162" t="n">
@@ -32173,6 +32164,9 @@
       <c r="O162" t="n">
         <v>0</v>
       </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
       <c r="R162" t="n">
         <v>0</v>
       </c>
@@ -32183,12 +32177,12 @@
       </c>
       <c r="U162" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO162" t="inlineStr">
@@ -32208,7 +32202,7 @@
       </c>
       <c r="AS162" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT162" t="n">
@@ -32221,42 +32215,42 @@
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32288,12 +32282,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -32318,12 +32312,12 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-28</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="N163" t="n">
@@ -32332,24 +32326,27 @@
       <c r="O163" t="n">
         <v>0</v>
       </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
       <c r="U163" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V163" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W163" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X163" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y163" t="inlineStr">
@@ -32364,7 +32361,7 @@
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB163" t="inlineStr">
@@ -32374,7 +32371,7 @@
       </c>
       <c r="AC163" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD163" t="inlineStr">
@@ -32409,17 +32406,17 @@
       </c>
       <c r="AJ163" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK163" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -32442,7 +32439,7 @@
       </c>
       <c r="AS163" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT163" t="n">
@@ -32455,42 +32452,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -32522,12 +32519,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -32561,13 +32558,13 @@
         </is>
       </c>
       <c r="N164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O164" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R164" t="n">
-        <v>0.03557618341728275</v>
+        <v>0</v>
       </c>
       <c r="S164" t="inlineStr">
         <is>
@@ -32576,7 +32573,7 @@
       </c>
       <c r="U164" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -32586,7 +32583,7 @@
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP164" t="inlineStr">
@@ -32596,12 +32593,12 @@
       </c>
       <c r="AQ164" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS164" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT164" t="n">
@@ -32609,47 +32606,47 @@
       </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32681,12 +32678,12 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
@@ -32720,29 +32717,29 @@
         </is>
       </c>
       <c r="N165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U165" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V165" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W165" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X165" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y165" t="inlineStr">
@@ -32752,7 +32749,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -32767,7 +32764,7 @@
       </c>
       <c r="AC165" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD165" t="inlineStr">
@@ -32802,17 +32799,17 @@
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -32820,7 +32817,7 @@
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP165" t="inlineStr">
@@ -32830,12 +32827,12 @@
       </c>
       <c r="AQ165" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS165" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT165" t="n">
@@ -32843,47 +32840,47 @@
       </c>
       <c r="AU165" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA165" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB165" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC165" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -32915,12 +32912,12 @@
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -32954,13 +32951,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R166" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -32969,7 +32966,7 @@
       </c>
       <c r="U166" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
@@ -32989,12 +32986,12 @@
       </c>
       <c r="AQ166" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS166" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT166" t="n">
@@ -33002,47 +32999,47 @@
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33074,12 +33071,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -33113,29 +33110,29 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V167" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W167" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X167" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y167" t="inlineStr">
@@ -33145,7 +33142,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -33160,7 +33157,7 @@
       </c>
       <c r="AC167" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD167" t="inlineStr">
@@ -33195,12 +33192,12 @@
       </c>
       <c r="AJ167" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK167" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM167" t="inlineStr">
@@ -33223,12 +33220,12 @@
       </c>
       <c r="AQ167" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS167" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT167" t="n">
@@ -33236,47 +33233,47 @@
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -33308,12 +33305,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -33353,7 +33350,7 @@
         <v>1</v>
       </c>
       <c r="R168" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -33362,7 +33359,7 @@
       </c>
       <c r="U168" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
@@ -33387,7 +33384,7 @@
       </c>
       <c r="AS168" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT168" t="n">
@@ -33400,42 +33397,42 @@
       </c>
       <c r="AV168" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA168" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB168" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC168" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33467,12 +33464,12 @@
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -33513,22 +33510,22 @@
       </c>
       <c r="U169" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V169" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W169" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X169" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y169" t="inlineStr">
@@ -33538,7 +33535,7 @@
       </c>
       <c r="Z169" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
@@ -33553,7 +33550,7 @@
       </c>
       <c r="AC169" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD169" t="inlineStr">
@@ -33588,17 +33585,17 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM169" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN169" t="b">
@@ -33621,7 +33618,7 @@
       </c>
       <c r="AS169" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT169" t="n">
@@ -33634,42 +33631,42 @@
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -33701,12 +33698,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -33746,7 +33743,7 @@
         <v>1</v>
       </c>
       <c r="R170" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -33755,7 +33752,7 @@
       </c>
       <c r="U170" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -33780,7 +33777,7 @@
       </c>
       <c r="AS170" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT170" t="n">
@@ -33793,42 +33790,42 @@
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -33860,12 +33857,12 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
@@ -33906,17 +33903,17 @@
       </c>
       <c r="U171" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V171" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W171" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X171" t="inlineStr">
@@ -33946,7 +33943,7 @@
       </c>
       <c r="AC171" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD171" t="inlineStr">
@@ -33981,17 +33978,17 @@
       </c>
       <c r="AJ171" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK171" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM171" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN171" t="b">
@@ -34014,7 +34011,7 @@
       </c>
       <c r="AS171" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT171" t="n">
@@ -34027,42 +34024,42 @@
       </c>
       <c r="AV171" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA171" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB171" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC171" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -34094,12 +34091,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -34124,7 +34121,7 @@
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M172" t="inlineStr">
@@ -34138,11 +34135,8 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
-      <c r="P172" t="n">
-        <v>1</v>
-      </c>
       <c r="R172" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -34151,17 +34145,17 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP172" t="inlineStr">
@@ -34171,12 +34165,12 @@
       </c>
       <c r="AQ172" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT172" t="n">
@@ -34184,47 +34178,47 @@
       </c>
       <c r="AU172" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34256,12 +34250,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -34286,7 +34280,7 @@
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
@@ -34300,27 +34294,24 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="P173" t="n">
-        <v>1</v>
-      </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -34330,12 +34321,12 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB173" t="inlineStr">
@@ -34345,7 +34336,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -34380,17 +34371,17 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34398,7 +34389,7 @@
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP173" t="inlineStr">
@@ -34408,12 +34399,12 @@
       </c>
       <c r="AQ173" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT173" t="n">
@@ -34421,47 +34412,47 @@
       </c>
       <c r="AU173" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34523,7 +34514,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -34532,16 +34523,16 @@
         </is>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R174" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -34685,7 +34676,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -34694,13 +34685,13 @@
         </is>
       </c>
       <c r="N175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
@@ -34892,12 +34883,12 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
@@ -34922,7 +34913,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -34931,16 +34922,16 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P176" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R176" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -34949,7 +34940,7 @@
       </c>
       <c r="U176" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA176" t="inlineStr">
@@ -34959,7 +34950,7 @@
       </c>
       <c r="AO176" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP176" t="inlineStr">
@@ -34969,12 +34960,12 @@
       </c>
       <c r="AQ176" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS176" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT176" t="n">
@@ -34982,47 +34973,47 @@
       </c>
       <c r="AU176" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV176" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW176" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX176" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY176" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ176" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA176" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB176" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC176" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35054,12 +35045,12 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
@@ -35084,7 +35075,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -35093,32 +35084,32 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P177" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V177" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W177" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X177" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y177" t="inlineStr">
@@ -35143,7 +35134,7 @@
       </c>
       <c r="AC177" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD177" t="inlineStr">
@@ -35178,12 +35169,12 @@
       </c>
       <c r="AJ177" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK177" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM177" t="inlineStr">
@@ -35196,7 +35187,7 @@
       </c>
       <c r="AO177" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP177" t="inlineStr">
@@ -35206,12 +35197,12 @@
       </c>
       <c r="AQ177" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS177" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT177" t="n">
@@ -35219,47 +35210,47 @@
       </c>
       <c r="AU177" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV177" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW177" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX177" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY177" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ177" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA177" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB177" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC177" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35291,12 +35282,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -35321,7 +35312,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -35330,16 +35321,16 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P178" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R178" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -35348,7 +35339,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -35358,7 +35349,7 @@
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
@@ -35368,12 +35359,12 @@
       </c>
       <c r="AQ178" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT178" t="n">
@@ -35381,47 +35372,47 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35453,12 +35444,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -35483,7 +35474,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -35492,32 +35483,32 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P179" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr">
@@ -35542,7 +35533,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -35577,12 +35568,12 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
@@ -35595,7 +35586,7 @@
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
@@ -35605,12 +35596,12 @@
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT179" t="n">
@@ -35618,47 +35609,47 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35720,7 +35711,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -35882,7 +35873,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -36089,12 +36080,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -36119,12 +36110,12 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N182" t="n">
@@ -36133,6 +36124,9 @@
       <c r="O182" t="n">
         <v>0</v>
       </c>
+      <c r="P182" t="n">
+        <v>0</v>
+      </c>
       <c r="R182" t="n">
         <v>0</v>
       </c>
@@ -36143,12 +36137,12 @@
       </c>
       <c r="U182" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA182" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO182" t="inlineStr">
@@ -36168,7 +36162,7 @@
       </c>
       <c r="AS182" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT182" t="n">
@@ -36181,42 +36175,42 @@
       </c>
       <c r="AV182" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW182" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX182" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY182" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ182" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA182" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB182" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC182" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36248,12 +36242,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -36278,12 +36272,12 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N183" t="n">
@@ -36292,24 +36286,27 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
+      <c r="P183" t="n">
+        <v>0</v>
+      </c>
       <c r="U183" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V183" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W183" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X183" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y183" t="inlineStr">
@@ -36324,7 +36321,7 @@
       </c>
       <c r="AA183" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB183" t="inlineStr">
@@ -36334,7 +36331,7 @@
       </c>
       <c r="AC183" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD183" t="inlineStr">
@@ -36369,17 +36366,17 @@
       </c>
       <c r="AJ183" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK183" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM183" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN183" t="b">
@@ -36402,7 +36399,7 @@
       </c>
       <c r="AS183" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT183" t="n">
@@ -36415,42 +36412,42 @@
       </c>
       <c r="AV183" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW183" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX183" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY183" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ183" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA183" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB183" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC183" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36482,12 +36479,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -36536,7 +36533,7 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
@@ -36546,7 +36543,7 @@
       </c>
       <c r="AO184" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP184" t="inlineStr">
@@ -36556,12 +36553,12 @@
       </c>
       <c r="AQ184" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT184" t="n">
@@ -36569,47 +36566,47 @@
       </c>
       <c r="AU184" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36641,12 +36638,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -36687,22 +36684,22 @@
       </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
@@ -36712,7 +36709,7 @@
       </c>
       <c r="Z185" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA185" t="inlineStr">
@@ -36727,7 +36724,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -36762,17 +36759,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -36780,7 +36777,7 @@
       </c>
       <c r="AO185" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP185" t="inlineStr">
@@ -36790,12 +36787,12 @@
       </c>
       <c r="AQ185" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT185" t="n">
@@ -36803,47 +36800,47 @@
       </c>
       <c r="AU185" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -36875,12 +36872,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -36929,7 +36926,7 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -36949,12 +36946,12 @@
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT186" t="n">
@@ -36962,47 +36959,47 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37034,12 +37031,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -37080,22 +37077,22 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
@@ -37105,7 +37102,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -37120,7 +37117,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -37155,12 +37152,12 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
@@ -37183,12 +37180,12 @@
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT187" t="n">
@@ -37196,47 +37193,47 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37268,12 +37265,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -37322,7 +37319,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -37347,7 +37344,7 @@
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT188" t="n">
@@ -37360,42 +37357,42 @@
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37427,12 +37424,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -37473,22 +37470,22 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -37498,7 +37495,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -37513,7 +37510,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -37548,17 +37545,17 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN189" t="b">
@@ -37581,7 +37578,7 @@
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT189" t="n">
@@ -37594,42 +37591,42 @@
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37661,12 +37658,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -37700,16 +37697,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1</v>
-      </c>
-      <c r="P190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -37718,12 +37712,12 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO190" t="inlineStr">
@@ -37743,7 +37737,7 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT190" t="n">
@@ -37756,42 +37750,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -37823,12 +37817,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -37862,32 +37856,29 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>1</v>
-      </c>
-      <c r="P191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -37897,12 +37888,12 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB191" t="inlineStr">
@@ -37912,7 +37903,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -37947,17 +37938,17 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -37980,7 +37971,7 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -37993,42 +37984,42 @@
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38060,12 +38051,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -38090,7 +38081,7 @@
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M192" t="inlineStr">
@@ -38099,16 +38090,16 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P192" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R192" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -38117,7 +38108,7 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
@@ -38127,7 +38118,7 @@
       </c>
       <c r="AO192" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP192" t="inlineStr">
@@ -38137,12 +38128,12 @@
       </c>
       <c r="AQ192" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT192" t="n">
@@ -38150,47 +38141,47 @@
       </c>
       <c r="AU192" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38222,210 +38213,609 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N193" t="n">
+        <v>1</v>
+      </c>
+      <c r="O193" t="n">
+        <v>1</v>
+      </c>
+      <c r="P193" t="n">
+        <v>1</v>
+      </c>
+      <c r="U193" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V193" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W193" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X193" t="inlineStr">
+        <is>
+          <t>Salmonella Paratyphi infection</t>
+        </is>
+      </c>
+      <c r="Y193" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB193" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD193" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE193" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF193" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG193" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH193" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI193" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ193" t="inlineStr">
+        <is>
+          <t>US_NNDSS_Paratyphi_current</t>
+        </is>
+      </c>
+      <c r="AK193" t="inlineStr">
+        <is>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+        </is>
+      </c>
+      <c r="AM193" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN193" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO193" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP193" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ193" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS193" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT193" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU193" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV193" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW193" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX193" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY193" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA193" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB193" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC193" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G193" t="inlineStr">
+      <c r="G194" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
+      <c r="H194" t="inlineStr">
         <is>
           <t>D234</t>
         </is>
       </c>
-      <c r="I193" t="inlineStr">
-        <is>
-          <t>Paratyphoid fever</t>
-        </is>
-      </c>
-      <c r="J193" t="inlineStr">
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
         <is>
           <t>副伤寒</t>
         </is>
       </c>
-      <c r="K193" t="inlineStr">
+      <c r="K194" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="L194" t="inlineStr">
         <is>
           <t>2026-08-02</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr">
+      <c r="M194" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N193" t="n">
+      <c r="N194" t="n">
         <v>0</v>
       </c>
-      <c r="O193" t="n">
+      <c r="O194" t="n">
         <v>0</v>
       </c>
-      <c r="P193" t="n">
+      <c r="P194" t="n">
         <v>0</v>
       </c>
-      <c r="U193" t="inlineStr">
+      <c r="R194" t="n">
+        <v>0</v>
+      </c>
+      <c r="S194" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U194" t="inlineStr">
         <is>
           <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
-      <c r="V193" t="inlineStr">
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO194" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP194" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ194" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS194" t="inlineStr">
         <is>
           <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
-      <c r="W193" t="inlineStr">
+      <c r="AT194" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU194" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV194" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW194" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX194" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY194" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA194" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB194" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC194" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M195" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="O195" t="n">
+        <v>0</v>
+      </c>
+      <c r="P195" t="n">
+        <v>0</v>
+      </c>
+      <c r="U195" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V195" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W195" t="inlineStr">
         <is>
           <t>SRC_JP_NIID</t>
         </is>
       </c>
-      <c r="X193" t="inlineStr">
-        <is>
-          <t>Paratyphoid fever</t>
-        </is>
-      </c>
-      <c r="Y193" t="inlineStr">
+      <c r="X195" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y195" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z193" t="inlineStr">
+      <c r="Z195" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA193" t="inlineStr">
+      <c r="AA195" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB193" t="inlineStr">
+      <c r="AB195" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC193" t="inlineStr">
+      <c r="AC195" t="inlineStr">
         <is>
           <t>country:JP:national</t>
         </is>
       </c>
-      <c r="AD193" t="inlineStr">
+      <c r="AD195" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE193" t="inlineStr">
+      <c r="AE195" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF193" t="inlineStr">
+      <c r="AF195" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG193" t="inlineStr">
+      <c r="AG195" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH193" t="inlineStr">
+      <c r="AH195" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI193" t="inlineStr">
+      <c r="AI195" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ193" t="inlineStr">
+      <c r="AJ195" t="inlineStr">
         <is>
           <t>JP_NIID_current</t>
         </is>
       </c>
-      <c r="AK193" t="inlineStr">
+      <c r="AK195" t="inlineStr">
         <is>
           <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
-      <c r="AM193" t="inlineStr">
+      <c r="AM195" t="inlineStr">
         <is>
           <t>provisional</t>
         </is>
       </c>
-      <c r="AN193" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO193" t="inlineStr">
+      <c r="AN195" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO195" t="inlineStr">
         <is>
           <t>mixed</t>
         </is>
       </c>
-      <c r="AP193" t="inlineStr">
+      <c r="AP195" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ193" t="inlineStr">
+      <c r="AQ195" t="inlineStr">
         <is>
           <t>legacy_gap_fill</t>
         </is>
       </c>
-      <c r="AS193" t="inlineStr">
+      <c r="AS195" t="inlineStr">
         <is>
           <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
-      <c r="AT193" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU193" t="inlineStr">
+      <c r="AT195" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU195" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
-      <c r="AV193" t="inlineStr">
+      <c r="AV195" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW193" t="inlineStr">
+      <c r="AW195" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX193" t="inlineStr">
+      <c r="AX195" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY193" t="inlineStr">
+      <c r="AY195" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ193" t="inlineStr">
+      <c r="AZ195" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA193" t="inlineStr">
+      <c r="BA195" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB193" t="inlineStr">
+      <c r="BB195" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC193" t="inlineStr">
+      <c r="BC195" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -38547,7 +38937,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -38557,7 +38947,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="11">
@@ -38577,7 +38967,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="13">
@@ -38609,7 +38999,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -38821,6 +38821,405 @@
         </is>
       </c>
     </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M196" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N196" t="n">
+        <v>0</v>
+      </c>
+      <c r="O196" t="n">
+        <v>0</v>
+      </c>
+      <c r="P196" t="n">
+        <v>0</v>
+      </c>
+      <c r="R196" t="n">
+        <v>0</v>
+      </c>
+      <c r="S196" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U196" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO196" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP196" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ196" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS196" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT196" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU196" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV196" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW196" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX196" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY196" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA196" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB196" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC196" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M197" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N197" t="n">
+        <v>0</v>
+      </c>
+      <c r="O197" t="n">
+        <v>0</v>
+      </c>
+      <c r="P197" t="n">
+        <v>0</v>
+      </c>
+      <c r="U197" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V197" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W197" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X197" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y197" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB197" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD197" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE197" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF197" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG197" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH197" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI197" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ197" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK197" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM197" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN197" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO197" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP197" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ197" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS197" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT197" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU197" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV197" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW197" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX197" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY197" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA197" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB197" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC197" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38854,7 +39253,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -38937,7 +39336,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="10">
@@ -38947,7 +39346,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="11">
@@ -38967,7 +39366,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -26875,7 +26875,7 @@
       </c>
       <c r="AM135" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN135" t="b">
@@ -32809,7 +32809,7 @@
       </c>
       <c r="AM165" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN165" t="b">
@@ -36769,7 +36769,7 @@
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>raw</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN185" t="b">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -32951,13 +32951,13 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O166" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R166" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S166" t="inlineStr">
         <is>
@@ -33110,10 +33110,10 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O167" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
@@ -37697,13 +37697,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R190" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -37856,10 +37856,10 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O191" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
@@ -39217,6 +39217,405 @@
       <c r="BC197" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M198" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N198" t="n">
+        <v>2</v>
+      </c>
+      <c r="O198" t="n">
+        <v>2</v>
+      </c>
+      <c r="P198" t="n">
+        <v>2</v>
+      </c>
+      <c r="R198" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S198" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U198" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO198" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP198" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ198" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS198" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT198" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU198" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV198" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW198" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX198" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY198" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA198" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB198" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC198" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>2</v>
+      </c>
+      <c r="O199" t="n">
+        <v>2</v>
+      </c>
+      <c r="P199" t="n">
+        <v>2</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_US_NNDSS</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Salmonella Paratyphi infection</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:US:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>US_NNDSS_Paratyphi_current</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -39253,7 +39652,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-15</t>
         </is>
       </c>
     </row>
@@ -39336,7 +39735,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10">
@@ -39346,7 +39745,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="11">
@@ -39366,7 +39765,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="13">
@@ -39398,7 +39797,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -33344,13 +33344,13 @@
         </is>
       </c>
       <c r="N168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O168" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R168" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S168" t="inlineStr">
         <is>
@@ -33503,10 +33503,10 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O169" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
@@ -33737,13 +33737,13 @@
         </is>
       </c>
       <c r="N170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R170" t="n">
-        <v>0.01768975825795506</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S170" t="inlineStr">
         <is>
@@ -33896,10 +33896,10 @@
         </is>
       </c>
       <c r="N171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
@@ -34091,12 +34091,12 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
@@ -34136,7 +34136,7 @@
         <v>1</v>
       </c>
       <c r="R172" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S172" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
       </c>
       <c r="U172" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA172" t="inlineStr">
@@ -34170,7 +34170,7 @@
       </c>
       <c r="AS172" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT172" t="n">
@@ -34183,42 +34183,42 @@
       </c>
       <c r="AV172" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA172" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB172" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC172" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34250,12 +34250,12 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -34296,22 +34296,22 @@
       </c>
       <c r="U173" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V173" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W173" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X173" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y173" t="inlineStr">
@@ -34321,7 +34321,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -34336,7 +34336,7 @@
       </c>
       <c r="AC173" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD173" t="inlineStr">
@@ -34371,17 +34371,17 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
+          <t>New Zealand PHF Science paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM173" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN173" t="b">
@@ -34404,7 +34404,7 @@
       </c>
       <c r="AS173" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT173" t="n">
@@ -34417,42 +34417,42 @@
       </c>
       <c r="AV173" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW173" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX173" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY173" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ173" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA173" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB173" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC173" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -34484,12 +34484,12 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -34514,7 +34514,7 @@
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M174" t="inlineStr">
@@ -34528,11 +34528,8 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
-      <c r="P174" t="n">
-        <v>1</v>
-      </c>
       <c r="R174" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S174" t="inlineStr">
         <is>
@@ -34541,17 +34538,17 @@
       </c>
       <c r="U174" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AA174" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO174" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP174" t="inlineStr">
@@ -34561,12 +34558,12 @@
       </c>
       <c r="AQ174" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS174" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT174" t="n">
@@ -34574,47 +34571,47 @@
       </c>
       <c r="AU174" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ174" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA174" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB174" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC174" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34646,12 +34643,12 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
@@ -34676,7 +34673,7 @@
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M175" t="inlineStr">
@@ -34690,27 +34687,24 @@
       <c r="O175" t="n">
         <v>1</v>
       </c>
-      <c r="P175" t="n">
-        <v>1</v>
-      </c>
       <c r="U175" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="V175" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="W175" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X175" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y175" t="inlineStr">
@@ -34720,12 +34714,12 @@
       </c>
       <c r="Z175" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA175" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB175" t="inlineStr">
@@ -34735,7 +34729,7 @@
       </c>
       <c r="AC175" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD175" t="inlineStr">
@@ -34770,17 +34764,17 @@
       </c>
       <c r="AJ175" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK175" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
         </is>
       </c>
       <c r="AM175" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN175" t="b">
@@ -34788,7 +34782,7 @@
       </c>
       <c r="AO175" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP175" t="inlineStr">
@@ -34798,12 +34792,12 @@
       </c>
       <c r="AQ175" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS175" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT175" t="n">
@@ -34811,47 +34805,47 @@
       </c>
       <c r="AU175" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ175" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA175" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB175" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC175" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -34913,7 +34907,7 @@
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M176" t="inlineStr">
@@ -34922,16 +34916,16 @@
         </is>
       </c>
       <c r="N176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P176" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R176" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S176" t="inlineStr">
         <is>
@@ -35075,7 +35069,7 @@
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
@@ -35084,13 +35078,13 @@
         </is>
       </c>
       <c r="N177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -35282,12 +35276,12 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
@@ -35312,7 +35306,7 @@
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
@@ -35321,16 +35315,16 @@
         </is>
       </c>
       <c r="N178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P178" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R178" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S178" t="inlineStr">
         <is>
@@ -35339,7 +35333,7 @@
       </c>
       <c r="U178" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA178" t="inlineStr">
@@ -35349,7 +35343,7 @@
       </c>
       <c r="AO178" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP178" t="inlineStr">
@@ -35359,12 +35353,12 @@
       </c>
       <c r="AQ178" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS178" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT178" t="n">
@@ -35372,47 +35366,47 @@
       </c>
       <c r="AU178" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV178" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW178" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX178" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY178" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ178" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA178" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB178" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC178" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35444,12 +35438,12 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
@@ -35474,7 +35468,7 @@
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M179" t="inlineStr">
@@ -35483,32 +35477,32 @@
         </is>
       </c>
       <c r="N179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P179" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V179" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W179" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X179" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y179" t="inlineStr">
@@ -35533,7 +35527,7 @@
       </c>
       <c r="AC179" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD179" t="inlineStr">
@@ -35568,12 +35562,12 @@
       </c>
       <c r="AJ179" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK179" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM179" t="inlineStr">
@@ -35586,7 +35580,7 @@
       </c>
       <c r="AO179" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP179" t="inlineStr">
@@ -35596,12 +35590,12 @@
       </c>
       <c r="AQ179" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS179" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT179" t="n">
@@ -35609,47 +35603,47 @@
       </c>
       <c r="AU179" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV179" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY179" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ179" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA179" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB179" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC179" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -35681,12 +35675,12 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
@@ -35711,7 +35705,7 @@
       </c>
       <c r="L180" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M180" t="inlineStr">
@@ -35720,16 +35714,16 @@
         </is>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P180" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R180" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S180" t="inlineStr">
         <is>
@@ -35738,7 +35732,7 @@
       </c>
       <c r="U180" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA180" t="inlineStr">
@@ -35748,7 +35742,7 @@
       </c>
       <c r="AO180" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP180" t="inlineStr">
@@ -35758,12 +35752,12 @@
       </c>
       <c r="AQ180" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS180" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT180" t="n">
@@ -35771,47 +35765,47 @@
       </c>
       <c r="AU180" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ180" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA180" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB180" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC180" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -35843,12 +35837,12 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
@@ -35873,7 +35867,7 @@
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M181" t="inlineStr">
@@ -35882,32 +35876,32 @@
         </is>
       </c>
       <c r="N181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V181" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W181" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X181" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y181" t="inlineStr">
@@ -35932,7 +35926,7 @@
       </c>
       <c r="AC181" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD181" t="inlineStr">
@@ -35967,12 +35961,12 @@
       </c>
       <c r="AJ181" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK181" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM181" t="inlineStr">
@@ -35985,7 +35979,7 @@
       </c>
       <c r="AO181" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP181" t="inlineStr">
@@ -35995,12 +35989,12 @@
       </c>
       <c r="AQ181" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS181" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT181" t="n">
@@ -36008,47 +36002,47 @@
       </c>
       <c r="AU181" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV181" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW181" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX181" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY181" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ181" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA181" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB181" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC181" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -36110,7 +36104,7 @@
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M182" t="inlineStr">
@@ -36272,7 +36266,7 @@
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M183" t="inlineStr">
@@ -36479,12 +36473,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -36509,12 +36503,12 @@
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N184" t="n">
@@ -36523,6 +36517,9 @@
       <c r="O184" t="n">
         <v>0</v>
       </c>
+      <c r="P184" t="n">
+        <v>0</v>
+      </c>
       <c r="R184" t="n">
         <v>0</v>
       </c>
@@ -36533,12 +36530,12 @@
       </c>
       <c r="U184" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA184" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO184" t="inlineStr">
@@ -36558,7 +36555,7 @@
       </c>
       <c r="AS184" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT184" t="n">
@@ -36571,42 +36568,42 @@
       </c>
       <c r="AV184" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW184" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX184" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY184" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ184" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA184" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB184" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC184" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36638,12 +36635,12 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -36668,12 +36665,12 @@
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N185" t="n">
@@ -36682,24 +36679,27 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
+      <c r="P185" t="n">
+        <v>0</v>
+      </c>
       <c r="U185" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V185" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W185" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X185" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y185" t="inlineStr">
@@ -36714,7 +36714,7 @@
       </c>
       <c r="AA185" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB185" t="inlineStr">
@@ -36724,7 +36724,7 @@
       </c>
       <c r="AC185" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD185" t="inlineStr">
@@ -36759,17 +36759,17 @@
       </c>
       <c r="AJ185" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK185" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM185" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN185" t="b">
@@ -36792,7 +36792,7 @@
       </c>
       <c r="AS185" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT185" t="n">
@@ -36805,42 +36805,42 @@
       </c>
       <c r="AV185" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW185" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX185" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY185" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ185" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA185" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB185" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC185" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -36872,12 +36872,12 @@
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -36926,7 +36926,7 @@
       </c>
       <c r="U186" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA186" t="inlineStr">
@@ -36936,7 +36936,7 @@
       </c>
       <c r="AO186" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP186" t="inlineStr">
@@ -36946,12 +36946,12 @@
       </c>
       <c r="AQ186" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS186" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT186" t="n">
@@ -36959,47 +36959,47 @@
       </c>
       <c r="AU186" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV186" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW186" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX186" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY186" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ186" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA186" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB186" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC186" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37031,12 +37031,12 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
@@ -37077,22 +37077,22 @@
       </c>
       <c r="U187" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V187" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W187" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X187" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y187" t="inlineStr">
@@ -37102,7 +37102,7 @@
       </c>
       <c r="Z187" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA187" t="inlineStr">
@@ -37117,7 +37117,7 @@
       </c>
       <c r="AC187" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD187" t="inlineStr">
@@ -37152,12 +37152,12 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM187" t="inlineStr">
@@ -37170,7 +37170,7 @@
       </c>
       <c r="AO187" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP187" t="inlineStr">
@@ -37180,12 +37180,12 @@
       </c>
       <c r="AQ187" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS187" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT187" t="n">
@@ -37193,47 +37193,47 @@
       </c>
       <c r="AU187" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV187" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW187" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX187" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY187" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ187" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA187" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB187" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC187" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -37265,12 +37265,12 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -37319,7 +37319,7 @@
       </c>
       <c r="U188" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA188" t="inlineStr">
@@ -37339,12 +37339,12 @@
       </c>
       <c r="AQ188" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS188" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT188" t="n">
@@ -37352,47 +37352,47 @@
       </c>
       <c r="AU188" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV188" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW188" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX188" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY188" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ188" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA188" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB188" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC188" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37424,12 +37424,12 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
@@ -37470,22 +37470,22 @@
       </c>
       <c r="U189" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V189" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W189" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X189" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y189" t="inlineStr">
@@ -37495,7 +37495,7 @@
       </c>
       <c r="Z189" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA189" t="inlineStr">
@@ -37510,7 +37510,7 @@
       </c>
       <c r="AC189" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD189" t="inlineStr">
@@ -37545,12 +37545,12 @@
       </c>
       <c r="AJ189" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK189" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM189" t="inlineStr">
@@ -37573,12 +37573,12 @@
       </c>
       <c r="AQ189" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS189" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT189" t="n">
@@ -37586,47 +37586,47 @@
       </c>
       <c r="AU189" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ189" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA189" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB189" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC189" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -37658,12 +37658,12 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
@@ -37697,13 +37697,13 @@
         </is>
       </c>
       <c r="N190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R190" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S190" t="inlineStr">
         <is>
@@ -37712,7 +37712,7 @@
       </c>
       <c r="U190" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA190" t="inlineStr">
@@ -37737,7 +37737,7 @@
       </c>
       <c r="AS190" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT190" t="n">
@@ -37750,42 +37750,42 @@
       </c>
       <c r="AV190" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW190" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX190" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY190" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ190" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA190" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB190" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC190" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -37817,12 +37817,12 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
@@ -37856,29 +37856,29 @@
         </is>
       </c>
       <c r="N191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O191" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V191" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W191" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X191" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y191" t="inlineStr">
@@ -37888,7 +37888,7 @@
       </c>
       <c r="Z191" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA191" t="inlineStr">
@@ -37903,7 +37903,7 @@
       </c>
       <c r="AC191" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD191" t="inlineStr">
@@ -37938,17 +37938,17 @@
       </c>
       <c r="AJ191" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK191" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM191" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN191" t="b">
@@ -37971,7 +37971,7 @@
       </c>
       <c r="AS191" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT191" t="n">
@@ -37984,42 +37984,42 @@
       </c>
       <c r="AV191" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW191" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX191" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY191" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ191" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA191" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB191" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC191" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -38051,12 +38051,12 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
@@ -38090,16 +38090,13 @@
         </is>
       </c>
       <c r="N192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O192" t="n">
-        <v>1</v>
-      </c>
-      <c r="P192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R192" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S192" t="inlineStr">
         <is>
@@ -38108,12 +38105,12 @@
       </c>
       <c r="U192" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA192" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO192" t="inlineStr">
@@ -38133,7 +38130,7 @@
       </c>
       <c r="AS192" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT192" t="n">
@@ -38146,42 +38143,42 @@
       </c>
       <c r="AV192" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY192" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ192" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA192" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB192" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC192" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38213,12 +38210,12 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -38252,32 +38249,29 @@
         </is>
       </c>
       <c r="N193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O193" t="n">
-        <v>1</v>
-      </c>
-      <c r="P193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V193" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W193" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X193" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y193" t="inlineStr">
@@ -38287,12 +38281,12 @@
       </c>
       <c r="Z193" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA193" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB193" t="inlineStr">
@@ -38302,7 +38296,7 @@
       </c>
       <c r="AC193" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD193" t="inlineStr">
@@ -38337,17 +38331,17 @@
       </c>
       <c r="AJ193" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK193" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM193" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN193" t="b">
@@ -38370,7 +38364,7 @@
       </c>
       <c r="AS193" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT193" t="n">
@@ -38383,42 +38377,42 @@
       </c>
       <c r="AV193" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY193" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ193" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA193" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB193" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC193" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -38450,12 +38444,12 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -38480,7 +38474,7 @@
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
@@ -38489,16 +38483,16 @@
         </is>
       </c>
       <c r="N194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P194" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R194" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S194" t="inlineStr">
         <is>
@@ -38507,7 +38501,7 @@
       </c>
       <c r="U194" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA194" t="inlineStr">
@@ -38517,7 +38511,7 @@
       </c>
       <c r="AO194" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP194" t="inlineStr">
@@ -38527,12 +38521,12 @@
       </c>
       <c r="AQ194" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS194" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT194" t="n">
@@ -38540,47 +38534,47 @@
       </c>
       <c r="AU194" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ194" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA194" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB194" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC194" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38612,12 +38606,12 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
@@ -38642,7 +38636,7 @@
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M195" t="inlineStr">
@@ -38651,32 +38645,32 @@
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U195" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V195" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W195" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X195" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y195" t="inlineStr">
@@ -38701,7 +38695,7 @@
       </c>
       <c r="AC195" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD195" t="inlineStr">
@@ -38736,12 +38730,12 @@
       </c>
       <c r="AJ195" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK195" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM195" t="inlineStr">
@@ -38754,7 +38748,7 @@
       </c>
       <c r="AO195" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP195" t="inlineStr">
@@ -38764,12 +38758,12 @@
       </c>
       <c r="AQ195" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS195" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT195" t="n">
@@ -38777,47 +38771,47 @@
       </c>
       <c r="AU195" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ195" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA195" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB195" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC195" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -38879,7 +38873,7 @@
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
@@ -39041,7 +39035,7 @@
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M197" t="inlineStr">
@@ -39248,12 +39242,12 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -39278,7 +39272,7 @@
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M198" t="inlineStr">
@@ -39287,16 +39281,16 @@
         </is>
       </c>
       <c r="N198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P198" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R198" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S198" t="inlineStr">
         <is>
@@ -39305,7 +39299,7 @@
       </c>
       <c r="U198" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AA198" t="inlineStr">
@@ -39315,7 +39309,7 @@
       </c>
       <c r="AO198" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP198" t="inlineStr">
@@ -39325,12 +39319,12 @@
       </c>
       <c r="AQ198" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS198" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT198" t="n">
@@ -39338,47 +39332,47 @@
       </c>
       <c r="AU198" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV198" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY198" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ198" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA198" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB198" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC198" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39410,212 +39404,1010 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M199" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N199" t="n">
+        <v>0</v>
+      </c>
+      <c r="O199" t="n">
+        <v>0</v>
+      </c>
+      <c r="P199" t="n">
+        <v>0</v>
+      </c>
+      <c r="U199" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V199" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W199" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X199" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y199" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB199" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC199" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD199" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE199" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF199" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG199" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH199" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI199" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ199" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK199" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM199" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN199" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO199" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP199" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ199" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS199" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT199" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU199" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV199" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW199" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX199" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY199" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA199" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB199" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC199" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
           <t>US</t>
         </is>
       </c>
-      <c r="G199" t="inlineStr">
+      <c r="G200" t="inlineStr">
         <is>
           <t>United States</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
+      <c r="H200" t="inlineStr">
         <is>
           <t>D234</t>
         </is>
       </c>
-      <c r="I199" t="inlineStr">
-        <is>
-          <t>Paratyphoid fever</t>
-        </is>
-      </c>
-      <c r="J199" t="inlineStr">
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
         <is>
           <t>副伤寒</t>
         </is>
       </c>
-      <c r="K199" t="inlineStr">
+      <c r="K200" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
+      <c r="L200" t="inlineStr">
         <is>
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="M199" t="inlineStr">
+      <c r="M200" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N199" t="n">
+      <c r="N200" t="n">
         <v>2</v>
       </c>
-      <c r="O199" t="n">
+      <c r="O200" t="n">
         <v>2</v>
       </c>
-      <c r="P199" t="n">
+      <c r="P200" t="n">
         <v>2</v>
       </c>
-      <c r="U199" t="inlineStr">
+      <c r="R200" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S200" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U200" t="inlineStr">
         <is>
           <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
-      <c r="V199" t="inlineStr">
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO200" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP200" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ200" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS200" t="inlineStr">
         <is>
           <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
-      <c r="W199" t="inlineStr">
+      <c r="AT200" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU200" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series.</t>
+        </is>
+      </c>
+      <c r="AV200" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW200" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX200" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY200" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA200" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB200" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC200" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N201" t="n">
+        <v>2</v>
+      </c>
+      <c r="O201" t="n">
+        <v>2</v>
+      </c>
+      <c r="P201" t="n">
+        <v>2</v>
+      </c>
+      <c r="U201" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V201" t="inlineStr">
+        <is>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W201" t="inlineStr">
         <is>
           <t>SRC_US_NNDSS</t>
         </is>
       </c>
-      <c r="X199" t="inlineStr">
+      <c r="X201" t="inlineStr">
         <is>
           <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
-      <c r="Y199" t="inlineStr">
+      <c r="Y201" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z199" t="inlineStr">
+      <c r="Z201" t="inlineStr">
         <is>
           <t>notification</t>
         </is>
       </c>
-      <c r="AA199" t="inlineStr">
+      <c r="AA201" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB199" t="inlineStr">
+      <c r="AB201" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC199" t="inlineStr">
+      <c r="AC201" t="inlineStr">
         <is>
           <t>country:US:national</t>
         </is>
       </c>
-      <c r="AD199" t="inlineStr">
+      <c r="AD201" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE199" t="inlineStr">
+      <c r="AE201" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF199" t="inlineStr">
+      <c r="AF201" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG199" t="inlineStr">
+      <c r="AG201" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH199" t="inlineStr">
+      <c r="AH201" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI199" t="inlineStr">
+      <c r="AI201" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ199" t="inlineStr">
+      <c r="AJ201" t="inlineStr">
         <is>
           <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
-      <c r="AK199" t="inlineStr">
+      <c r="AK201" t="inlineStr">
         <is>
           <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
-      <c r="AM199" t="inlineStr">
+      <c r="AM201" t="inlineStr">
         <is>
           <t>provisional</t>
         </is>
       </c>
-      <c r="AN199" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO199" t="inlineStr">
+      <c r="AN201" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO201" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP199" t="inlineStr">
+      <c r="AP201" t="inlineStr">
         <is>
           <t>single_series</t>
         </is>
       </c>
-      <c r="AQ199" t="inlineStr">
+      <c r="AQ201" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS199" t="inlineStr">
+      <c r="AS201" t="inlineStr">
         <is>
           <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
-      <c r="AT199" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU199" t="inlineStr">
+      <c r="AT201" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU201" t="inlineStr">
         <is>
           <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
-      <c r="AV199" t="inlineStr">
+      <c r="AV201" t="inlineStr">
         <is>
           <t>nndss_api</t>
         </is>
       </c>
-      <c r="AW199" t="inlineStr">
+      <c r="AW201" t="inlineStr">
         <is>
           <t>US CDC NNDSS</t>
         </is>
       </c>
-      <c r="AX199" t="inlineStr">
+      <c r="AX201" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
-      <c r="AY199" t="inlineStr">
+      <c r="AY201" t="inlineStr">
         <is>
           <t>api</t>
         </is>
       </c>
-      <c r="AZ199" t="inlineStr">
+      <c r="AZ201" t="inlineStr">
         <is>
           <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
-      <c r="BA199" t="inlineStr">
+      <c r="BA201" t="inlineStr">
         <is>
           <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
-      <c r="BB199" t="inlineStr">
+      <c r="BB201" t="inlineStr">
         <is>
           <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
-      <c r="BC199" t="inlineStr">
+      <c r="BC201" t="inlineStr">
         <is>
           <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I202" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J202" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K202" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L202" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M202" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N202" t="n">
+        <v>0</v>
+      </c>
+      <c r="O202" t="n">
+        <v>0</v>
+      </c>
+      <c r="P202" t="n">
+        <v>0</v>
+      </c>
+      <c r="R202" t="n">
+        <v>0</v>
+      </c>
+      <c r="S202" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U202" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO202" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP202" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ202" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS202" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT202" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU202" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV202" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW202" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX202" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY202" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA202" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB202" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC202" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L203" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N203" t="n">
+        <v>0</v>
+      </c>
+      <c r="O203" t="n">
+        <v>0</v>
+      </c>
+      <c r="P203" t="n">
+        <v>0</v>
+      </c>
+      <c r="U203" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V203" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W203" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X203" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y203" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB203" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC203" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD203" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE203" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF203" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG203" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH203" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI203" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ203" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK203" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM203" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN203" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO203" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP203" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ203" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS203" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT203" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU203" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV203" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW203" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX203" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY203" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA203" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB203" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC203" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -39652,7 +40444,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -39735,7 +40527,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10">
@@ -39745,7 +40537,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11">
@@ -39765,7 +40557,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13">
@@ -39797,7 +40589,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d234/2026-2029.xlsx
+++ b/diseases/d234/2026-2029.xlsx
@@ -43549,12 +43549,12 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
@@ -43588,13 +43588,13 @@
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R220" t="n">
-        <v>0</v>
+        <v>0.01355270280196709</v>
       </c>
       <c r="S220" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
       </c>
       <c r="U220" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA220" t="inlineStr">
@@ -43613,7 +43613,7 @@
       </c>
       <c r="AO220" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP220" t="inlineStr">
@@ -43623,12 +43623,12 @@
       </c>
       <c r="AQ220" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS220" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT220" t="n">
@@ -43636,47 +43636,47 @@
       </c>
       <c r="AU220" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV220" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW220" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX220" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY220" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ220" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA220" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB220" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC220" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43708,12 +43708,12 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
@@ -43747,29 +43747,29 @@
         </is>
       </c>
       <c r="N221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O221" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U221" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V221" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W221" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_HK_CHP</t>
         </is>
       </c>
       <c r="X221" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y221" t="inlineStr">
@@ -43794,7 +43794,7 @@
       </c>
       <c r="AC221" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:HK:national</t>
         </is>
       </c>
       <c r="AD221" t="inlineStr">
@@ -43829,12 +43829,12 @@
       </c>
       <c r="AJ221" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>HK_CHP_current</t>
         </is>
       </c>
       <c r="AK221" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Hong Kong, China CHP paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM221" t="inlineStr">
@@ -43847,7 +43847,7 @@
       </c>
       <c r="AO221" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP221" t="inlineStr">
@@ -43857,12 +43857,12 @@
       </c>
       <c r="AQ221" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS221" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_HK_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT221" t="n">
@@ -43870,47 +43870,47 @@
       </c>
       <c r="AU221" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ221" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA221" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB221" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC221" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -43942,12 +43942,12 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
@@ -43981,13 +43981,13 @@
         </is>
       </c>
       <c r="N222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O222" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R222" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S222" t="inlineStr">
         <is>
@@ -43996,7 +43996,7 @@
       </c>
       <c r="U222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA222" t="inlineStr">
@@ -44021,7 +44021,7 @@
       </c>
       <c r="AS222" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT222" t="n">
@@ -44034,42 +44034,42 @@
       </c>
       <c r="AV222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ222" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA222" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB222" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC222" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -44101,12 +44101,12 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
@@ -44140,29 +44140,29 @@
         </is>
       </c>
       <c r="N223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O223" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U223" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V223" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W223" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X223" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y223" t="inlineStr">
@@ -44172,7 +44172,7 @@
       </c>
       <c r="Z223" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
@@ -44187,7 +44187,7 @@
       </c>
       <c r="AC223" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD223" t="inlineStr">
@@ -44222,17 +44222,17 @@
       </c>
       <c r="AJ223" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM223" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN223" t="b">
@@ -44255,7 +44255,7 @@
       </c>
       <c r="AS223" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT223" t="n">
@@ -44268,42 +44268,42 @@
       </c>
       <c r="AV223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ223" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA223" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB223" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC223" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -44335,12 +44335,12 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
@@ -44374,13 +44374,13 @@
         </is>
       </c>
       <c r="N224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R224" t="n">
-        <v>0.01891260466471829</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S224" t="inlineStr">
         <is>
@@ -44389,7 +44389,7 @@
       </c>
       <c r="U224" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA224" t="inlineStr">
@@ -44414,7 +44414,7 @@
       </c>
       <c r="AS224" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT224" t="n">
@@ -44427,42 +44427,42 @@
       </c>
       <c r="AV224" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW224" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX224" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ224" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA224" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB224" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC224" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44494,12 +44494,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>NZ</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>New Zealand</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -44533,29 +44533,29 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U225" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V225" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W225" t="inlineStr">
         <is>
-          <t>SRC_NZ_PHS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X225" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y225" t="inlineStr">
@@ -44565,7 +44565,7 @@
       </c>
       <c r="Z225" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA225" t="inlineStr">
@@ -44580,7 +44580,7 @@
       </c>
       <c r="AC225" t="inlineStr">
         <is>
-          <t>country:NZ:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD225" t="inlineStr">
@@ -44615,17 +44615,17 @@
       </c>
       <c r="AJ225" t="inlineStr">
         <is>
-          <t>NZ_PHS_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK225" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science paratyphoid-only notifications.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM225" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN225" t="b">
@@ -44648,7 +44648,7 @@
       </c>
       <c r="AS225" t="inlineStr">
         <is>
-          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT225" t="n">
@@ -44661,42 +44661,42 @@
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>phf_monthly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://www.phfscience.nz/digital-library/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44728,12 +44728,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -44773,7 +44773,7 @@
         <v>1</v>
       </c>
       <c r="R226" t="n">
-        <v>0.009344880428283346</v>
+        <v>0.01891260466471829</v>
       </c>
       <c r="S226" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
       </c>
       <c r="U226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -44807,7 +44807,7 @@
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
@@ -44820,42 +44820,42 @@
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -44887,12 +44887,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NZ</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>New Zealand</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -44933,22 +44933,22 @@
       </c>
       <c r="U227" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V227" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W227" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NZ_PHS</t>
         </is>
       </c>
       <c r="X227" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y227" t="inlineStr">
@@ -44958,7 +44958,7 @@
       </c>
       <c r="Z227" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA227" t="inlineStr">
@@ -44973,7 +44973,7 @@
       </c>
       <c r="AC227" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NZ:national</t>
         </is>
       </c>
       <c r="AD227" t="inlineStr">
@@ -45008,17 +45008,17 @@
       </c>
       <c r="AJ227" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NZ_PHS_current</t>
         </is>
       </c>
       <c r="AK227" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
+          <t>New Zealand PHF Science paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM227" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN227" t="b">
@@ -45041,7 +45041,7 @@
       </c>
       <c r="AS227" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
+          <t>SER_NZ_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT227" t="n">
@@ -45054,42 +45054,42 @@
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>phf_monthly</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>New Zealand PHF Science Monthly Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phfscience.nz/digital-library/</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45121,12 +45121,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -45151,7 +45151,7 @@
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M228" t="inlineStr">
@@ -45165,11 +45165,8 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
-      <c r="P228" t="n">
-        <v>1</v>
-      </c>
       <c r="R228" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -45178,17 +45175,17 @@
       </c>
       <c r="U228" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AA228" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO228" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP228" t="inlineStr">
@@ -45198,12 +45195,12 @@
       </c>
       <c r="AQ228" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS228" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT228" t="n">
@@ -45211,47 +45208,47 @@
       </c>
       <c r="AU228" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ228" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA228" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45283,12 +45280,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -45313,7 +45310,7 @@
       </c>
       <c r="L229" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M229" t="inlineStr">
@@ -45327,27 +45324,24 @@
       <c r="O229" t="n">
         <v>1</v>
       </c>
-      <c r="P229" t="n">
-        <v>1</v>
-      </c>
       <c r="U229" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="V229" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="W229" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SE_FOHM_SMINET</t>
         </is>
       </c>
       <c r="X229" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y229" t="inlineStr">
@@ -45357,12 +45351,12 @@
       </c>
       <c r="Z229" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA229" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB229" t="inlineStr">
@@ -45372,7 +45366,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SE:national</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -45407,17 +45401,17 @@
       </c>
       <c r="AJ229" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SE_FOHM_SMINET_current</t>
         </is>
       </c>
       <c r="AK229" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Sweden FHM SmiNet national monthly notification series; Paratyphoid-only source category.</t>
         </is>
       </c>
       <c r="AM229" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>revised</t>
         </is>
       </c>
       <c r="AN229" t="b">
@@ -45425,7 +45419,7 @@
       </c>
       <c r="AO229" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP229" t="inlineStr">
@@ -45435,12 +45429,12 @@
       </c>
       <c r="AQ229" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS229" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SE_FOHM_SMINET_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT229" t="n">
@@ -45448,47 +45442,47 @@
       </c>
       <c r="AU229" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ229" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA229" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -45520,12 +45514,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -45568,13 +45562,18 @@
         <v>1</v>
       </c>
       <c r="R230" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U230" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA230" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -45582,70 +45581,70 @@
       </c>
       <c r="AO230" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ230" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS230" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU230" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ230" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA230" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45677,12 +45676,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -45726,22 +45725,22 @@
       </c>
       <c r="U231" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V231" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W231" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X231" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y231" t="inlineStr">
@@ -45751,7 +45750,7 @@
       </c>
       <c r="Z231" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA231" t="inlineStr">
@@ -45766,7 +45765,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -45801,17 +45800,17 @@
       </c>
       <c r="AJ231" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK231" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM231" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN231" t="b">
@@ -45819,70 +45818,70 @@
       </c>
       <c r="AO231" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ231" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS231" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT231" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU231" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ231" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA231" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45914,12 +45913,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -45944,7 +45943,7 @@
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M232" t="inlineStr">
@@ -45953,27 +45952,22 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P232" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R232" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U232" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA232" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -45981,70 +45975,70 @@
       </c>
       <c r="AO232" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ232" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS232" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU232" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ232" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA232" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46076,12 +46070,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -46106,7 +46100,7 @@
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M233" t="inlineStr">
@@ -46115,32 +46109,32 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V233" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W233" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X233" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y233" t="inlineStr">
@@ -46150,7 +46144,7 @@
       </c>
       <c r="Z233" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA233" t="inlineStr">
@@ -46165,7 +46159,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -46200,17 +46194,17 @@
       </c>
       <c r="AJ233" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK233" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM233" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN233" t="b">
@@ -46218,70 +46212,70 @@
       </c>
       <c r="AO233" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ233" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS233" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU233" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ233" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA233" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46313,12 +46307,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -46352,22 +46346,27 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P234" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R234" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA234" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -46375,70 +46374,70 @@
       </c>
       <c r="AO234" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ234" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS234" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT234" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU234" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV234" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW234" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX234" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY234" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ234" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA234" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46470,12 +46469,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -46509,32 +46508,32 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V235" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W235" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X235" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y235" t="inlineStr">
@@ -46544,7 +46543,7 @@
       </c>
       <c r="Z235" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA235" t="inlineStr">
@@ -46559,7 +46558,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -46594,17 +46593,17 @@
       </c>
       <c r="AJ235" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK235" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM235" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN235" t="b">
@@ -46612,70 +46611,70 @@
       </c>
       <c r="AO235" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ235" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS235" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT235" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU235" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ235" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA235" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46707,12 +46706,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -46737,7 +46736,7 @@
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M236" t="inlineStr">
@@ -46746,98 +46745,93 @@
         </is>
       </c>
       <c r="N236" t="n">
+        <v>1</v>
+      </c>
+      <c r="O236" t="n">
+        <v>1</v>
+      </c>
+      <c r="P236" t="n">
+        <v>1</v>
+      </c>
+      <c r="R236" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S236" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO236" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP236" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ236" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS236" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT236" t="n">
         <v>2</v>
       </c>
-      <c r="O236" t="n">
-        <v>2</v>
-      </c>
-      <c r="P236" t="n">
-        <v>2</v>
-      </c>
-      <c r="R236" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S236" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U236" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA236" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO236" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP236" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ236" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS236" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT236" t="n">
-        <v>1</v>
-      </c>
       <c r="AU236" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV236" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY236" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ236" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA236" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -46869,12 +46863,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -46899,7 +46893,7 @@
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M237" t="inlineStr">
@@ -46908,173 +46902,173 @@
         </is>
       </c>
       <c r="N237" t="n">
+        <v>1</v>
+      </c>
+      <c r="O237" t="n">
+        <v>1</v>
+      </c>
+      <c r="P237" t="n">
+        <v>1</v>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X237" t="inlineStr">
+        <is>
+          <t>Paratyphoid</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB237" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC237" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD237" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE237" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF237" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG237" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH237" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI237" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ237" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK237" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM237" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN237" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO237" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP237" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ237" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS237" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT237" t="n">
         <v>2</v>
       </c>
-      <c r="O237" t="n">
-        <v>2</v>
-      </c>
-      <c r="P237" t="n">
-        <v>2</v>
-      </c>
-      <c r="U237" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V237" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W237" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X237" t="inlineStr">
-        <is>
-          <t>Salmonella Paratyphi infection</t>
-        </is>
-      </c>
-      <c r="Y237" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z237" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA237" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB237" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC237" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD237" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE237" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF237" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG237" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH237" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI237" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ237" t="inlineStr">
-        <is>
-          <t>US_NNDSS_Paratyphi_current</t>
-        </is>
-      </c>
-      <c r="AK237" t="inlineStr">
-        <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
-        </is>
-      </c>
-      <c r="AM237" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN237" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO237" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP237" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ237" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS237" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT237" t="n">
-        <v>1</v>
-      </c>
       <c r="AU237" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV237" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY237" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ237" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA237" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -47106,12 +47100,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -47136,7 +47130,7 @@
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M238" t="inlineStr">
@@ -47145,16 +47139,16 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R238" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -47163,7 +47157,7 @@
       </c>
       <c r="U238" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA238" t="inlineStr">
@@ -47173,7 +47167,7 @@
       </c>
       <c r="AO238" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP238" t="inlineStr">
@@ -47183,12 +47177,12 @@
       </c>
       <c r="AQ238" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS238" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT238" t="n">
@@ -47196,47 +47190,47 @@
       </c>
       <c r="AU238" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ238" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA238" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47268,12 +47262,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -47298,7 +47292,7 @@
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M239" t="inlineStr">
@@ -47307,32 +47301,32 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P239" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V239" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W239" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X239" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y239" t="inlineStr">
@@ -47357,7 +47351,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr">
@@ -47392,12 +47386,12 @@
       </c>
       <c r="AJ239" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK239" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM239" t="inlineStr">
@@ -47410,7 +47404,7 @@
       </c>
       <c r="AO239" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP239" t="inlineStr">
@@ -47420,12 +47414,12 @@
       </c>
       <c r="AQ239" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS239" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT239" t="n">
@@ -47433,47 +47427,47 @@
       </c>
       <c r="AU239" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ239" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA239" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -47505,12 +47499,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -47544,22 +47538,27 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R240" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA240" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -47567,70 +47566,70 @@
       </c>
       <c r="AO240" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ240" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS240" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU240" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ240" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA240" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47662,12 +47661,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -47701,32 +47700,32 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P241" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V241" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W241" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X241" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y241" t="inlineStr">
@@ -47736,7 +47735,7 @@
       </c>
       <c r="Z241" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA241" t="inlineStr">
@@ -47751,7 +47750,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -47786,17 +47785,17 @@
       </c>
       <c r="AJ241" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK241" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM241" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN241" t="b">
@@ -47804,70 +47803,70 @@
       </c>
       <c r="AO241" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ241" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS241" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT241" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU241" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ241" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA241" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47899,12 +47898,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -47929,7 +47928,7 @@
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M242" t="inlineStr">
@@ -47938,27 +47937,22 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R242" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U242" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA242" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -47966,70 +47960,70 @@
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ242" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS242" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48061,12 +48055,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -48091,7 +48085,7 @@
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M243" t="inlineStr">
@@ -48100,32 +48094,32 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V243" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W243" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X243" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y243" t="inlineStr">
@@ -48135,7 +48129,7 @@
       </c>
       <c r="Z243" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA243" t="inlineStr">
@@ -48150,7 +48144,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -48185,17 +48179,17 @@
       </c>
       <c r="AJ243" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK243" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM243" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN243" t="b">
@@ -48203,70 +48197,70 @@
       </c>
       <c r="AO243" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ243" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48298,12 +48292,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -48353,6 +48347,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA244" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -48360,70 +48359,70 @@
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ244" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS244" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48455,12 +48454,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -48504,22 +48503,22 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V245" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W245" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X245" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y245" t="inlineStr">
@@ -48529,7 +48528,7 @@
       </c>
       <c r="Z245" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -48544,7 +48543,7 @@
       </c>
       <c r="AC245" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD245" t="inlineStr">
@@ -48579,17 +48578,17 @@
       </c>
       <c r="AJ245" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK245" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM245" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN245" t="b">
@@ -48597,70 +48596,70 @@
       </c>
       <c r="AO245" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48692,12 +48691,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -48722,12 +48721,12 @@
       </c>
       <c r="L246" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N246" t="n">
@@ -48736,6 +48735,9 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
+      <c r="P246" t="n">
+        <v>0</v>
+      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -48744,82 +48746,77 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
-        </is>
-      </c>
       <c r="AA246" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ246" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -48851,12 +48848,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -48881,12 +48878,12 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N247" t="n">
@@ -48895,19 +48892,22 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
+      <c r="P247" t="n">
+        <v>0</v>
+      </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V247" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W247" t="inlineStr">
         <is>
-          <t>SRC_AU_NINDSS</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X247" t="inlineStr">
@@ -48922,12 +48922,12 @@
       </c>
       <c r="Z247" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
         <is>
-          <t>monthly</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AB247" t="inlineStr">
@@ -48937,7 +48937,7 @@
       </c>
       <c r="AC247" t="inlineStr">
         <is>
-          <t>country:AU:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD247" t="inlineStr">
@@ -48972,12 +48972,12 @@
       </c>
       <c r="AJ247" t="inlineStr">
         <is>
-          <t>AU_NINDSS_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK247" t="inlineStr">
         <is>
-          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM247" t="inlineStr">
@@ -48990,70 +48990,70 @@
       </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ247" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_AU_PARATYPHOID_MONTHLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -49085,12 +49085,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -49139,7 +49139,7 @@
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA248" t="inlineStr">
@@ -49149,7 +49149,7 @@
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
@@ -49159,12 +49159,12 @@
       </c>
       <c r="AQ248" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -49172,47 +49172,47 @@
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -49244,12 +49244,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -49290,22 +49290,22 @@
       </c>
       <c r="U249" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V249" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W249" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_AU_NINDSS</t>
         </is>
       </c>
       <c r="X249" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y249" t="inlineStr">
@@ -49315,7 +49315,7 @@
       </c>
       <c r="Z249" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA249" t="inlineStr">
@@ -49330,7 +49330,7 @@
       </c>
       <c r="AC249" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:AU:national</t>
         </is>
       </c>
       <c r="AD249" t="inlineStr">
@@ -49365,12 +49365,12 @@
       </c>
       <c r="AJ249" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>AU_NINDSS_current</t>
         </is>
       </c>
       <c r="AK249" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
+          <t>Australia NINDSS paratyphoid-only notifications; excludes typhoid fever.</t>
         </is>
       </c>
       <c r="AM249" t="inlineStr">
@@ -49383,7 +49383,7 @@
       </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
@@ -49393,12 +49393,12 @@
       </c>
       <c r="AQ249" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS249" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1190</t>
+          <t>SER_AU_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT249" t="n">
@@ -49406,47 +49406,47 @@
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -49478,12 +49478,12 @@
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -49532,7 +49532,7 @@
       </c>
       <c r="U250" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AA250" t="inlineStr">
@@ -49552,12 +49552,12 @@
       </c>
       <c r="AQ250" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS250" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT250" t="n">
@@ -49565,47 +49565,47 @@
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -49637,12 +49637,12 @@
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
@@ -49683,22 +49683,22 @@
       </c>
       <c r="U251" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="V251" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="W251" t="inlineStr">
         <is>
-          <t>SRC_KR_KDCA</t>
+          <t>SRC_FI_THL_TTR</t>
         </is>
       </c>
       <c r="X251" t="inlineStr">
         <is>
-          <t>파라티푸스</t>
+          <t>Salmonella Paratyphi</t>
         </is>
       </c>
       <c r="Y251" t="inlineStr">
@@ -49708,7 +49708,7 @@
       </c>
       <c r="Z251" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA251" t="inlineStr">
@@ -49723,7 +49723,7 @@
       </c>
       <c r="AC251" t="inlineStr">
         <is>
-          <t>country:KR:national</t>
+          <t>country:FI:national</t>
         </is>
       </c>
       <c r="AD251" t="inlineStr">
@@ -49758,12 +49758,12 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>KR_KDCA_current</t>
+          <t>FI_THL_TTR_reporting_group</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
         <is>
-          <t>Korea KDCA paratyphoid-only notifications.</t>
+          <t>Finland THL national monthly notification series; Paratyphi-only series.</t>
         </is>
       </c>
       <c r="AM251" t="inlineStr">
@@ -49786,12 +49786,12 @@
       </c>
       <c r="AQ251" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS251" t="inlineStr">
         <is>
-          <t>SER_KR_PARATYPHOID_MONTHLY</t>
+          <t>SER_FI_THL_TTR_1190</t>
         </is>
       </c>
       <c r="AT251" t="n">
@@ -49799,47 +49799,47 @@
       </c>
       <c r="AU251" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV251" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW251" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX251" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY251" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ251" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA251" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB251" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC251" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -49871,12 +49871,12 @@
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
@@ -49910,13 +49910,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0.03537951651591013</v>
+        <v>0</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -49925,7 +49925,7 @@
       </c>
       <c r="U252" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AA252" t="inlineStr">
@@ -49950,7 +49950,7 @@
       </c>
       <c r="AS252" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT252" t="n">
@@ -49963,42 +49963,42 @@
       </c>
       <c r="AV252" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW252" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX252" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY252" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ252" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA252" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB252" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC252" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -50030,12 +50030,12 @@
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
@@ -50069,29 +50069,29 @@
         </is>
       </c>
       <c r="N253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O253" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U253" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="V253" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="W253" t="inlineStr">
         <is>
-          <t>SRC_NO_FHI_MSIS</t>
+          <t>SRC_KR_KDCA</t>
         </is>
       </c>
       <c r="X253" t="inlineStr">
         <is>
-          <t>Paratyfoidfeber</t>
+          <t>파라티푸스</t>
         </is>
       </c>
       <c r="Y253" t="inlineStr">
@@ -50101,7 +50101,7 @@
       </c>
       <c r="Z253" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA253" t="inlineStr">
@@ -50116,7 +50116,7 @@
       </c>
       <c r="AC253" t="inlineStr">
         <is>
-          <t>country:NO:national</t>
+          <t>country:KR:national</t>
         </is>
       </c>
       <c r="AD253" t="inlineStr">
@@ -50151,17 +50151,17 @@
       </c>
       <c r="AJ253" t="inlineStr">
         <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+          <t>KR_KDCA_current</t>
         </is>
       </c>
       <c r="AK253" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
+          <t>Korea KDCA paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM253" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN253" t="b">
@@ -50184,7 +50184,7 @@
       </c>
       <c r="AS253" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_705_MONTHLY</t>
+          <t>SER_KR_PARATYPHOID_MONTHLY</t>
         </is>
       </c>
       <c r="AT253" t="n">
@@ -50197,42 +50197,42 @@
       </c>
       <c r="AV253" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW253" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX253" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY253" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ253" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA253" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB253" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC253" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -50264,12 +50264,12 @@
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
@@ -50303,16 +50303,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O254" t="n">
-        <v>1</v>
-      </c>
-      <c r="P254" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R254" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.03537951651591013</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -50321,12 +50318,12 @@
       </c>
       <c r="U254" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AA254" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO254" t="inlineStr">
@@ -50346,7 +50343,7 @@
       </c>
       <c r="AS254" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT254" t="n">
@@ -50359,42 +50356,42 @@
       </c>
       <c r="AV254" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY254" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ254" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA254" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB254" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC254" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -50426,12 +50423,12 @@
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
@@ -50465,32 +50462,29 @@
         </is>
       </c>
       <c r="N255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O255" t="n">
-        <v>1</v>
-      </c>
-      <c r="P255" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U255" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="V255" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="W255" t="inlineStr">
         <is>
-          <t>SRC_US_NNDSS</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X255" t="inlineStr">
         <is>
-          <t>Salmonella Paratyphi infection</t>
+          <t>Paratyfoidfeber</t>
         </is>
       </c>
       <c r="Y255" t="inlineStr">
@@ -50500,12 +50494,12 @@
       </c>
       <c r="Z255" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA255" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AB255" t="inlineStr">
@@ -50515,7 +50509,7 @@
       </c>
       <c r="AC255" t="inlineStr">
         <is>
-          <t>country:US:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD255" t="inlineStr">
@@ -50550,17 +50544,17 @@
       </c>
       <c r="AJ255" t="inlineStr">
         <is>
-          <t>US_NNDSS_Paratyphi_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK255" t="inlineStr">
         <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS paratyphoid-only category.</t>
         </is>
       </c>
       <c r="AM255" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN255" t="b">
@@ -50583,7 +50577,7 @@
       </c>
       <c r="AS255" t="inlineStr">
         <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
+          <t>SER_NO_FHI_705_MONTHLY</t>
         </is>
       </c>
       <c r="AT255" t="n">
@@ -50596,42 +50590,42 @@
       </c>
       <c r="AV255" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY255" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ255" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA255" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB255" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC255" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -50663,12 +50657,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -50693,7 +50687,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -50702,16 +50696,16 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R256" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -50720,7 +50714,7 @@
       </c>
       <c r="U256" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA256" t="inlineStr">
@@ -50730,7 +50724,7 @@
       </c>
       <c r="AO256" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP256" t="inlineStr">
@@ -50740,12 +50734,12 @@
       </c>
       <c r="AQ256" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS256" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT256" t="n">
@@ -50753,47 +50747,47 @@
       </c>
       <c r="AU256" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -50825,12 +50819,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -50855,7 +50849,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -50864,32 +50858,32 @@
         </is>
       </c>
       <c r="N257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U257" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V257" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W257" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X257" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y257" t="inlineStr">
@@ -50914,7 +50908,7 @@
       </c>
       <c r="AC257" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD257" t="inlineStr">
@@ -50949,12 +50943,12 @@
       </c>
       <c r="AJ257" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK257" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM257" t="inlineStr">
@@ -50967,7 +50961,7 @@
       </c>
       <c r="AO257" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP257" t="inlineStr">
@@ -50977,12 +50971,12 @@
       </c>
       <c r="AQ257" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS257" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT257" t="n">
@@ -50990,47 +50984,47 @@
       </c>
       <c r="AU257" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -51062,12 +51056,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -51101,22 +51095,27 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P258" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R258" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA258" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -51124,70 +51123,70 @@
       </c>
       <c r="AO258" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP258" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ258" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS258" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT258" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU258" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51219,12 +51218,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -51258,32 +51257,32 @@
         </is>
       </c>
       <c r="N259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U259" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V259" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W259" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X259" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y259" t="inlineStr">
@@ -51293,7 +51292,7 @@
       </c>
       <c r="Z259" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA259" t="inlineStr">
@@ -51308,7 +51307,7 @@
       </c>
       <c r="AC259" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD259" t="inlineStr">
@@ -51343,17 +51342,17 @@
       </c>
       <c r="AJ259" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK259" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM259" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN259" t="b">
@@ -51361,70 +51360,70 @@
       </c>
       <c r="AO259" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP259" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ259" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS259" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT259" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU259" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -51456,12 +51455,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -51486,7 +51485,7 @@
       </c>
       <c r="L260" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M260" t="inlineStr">
@@ -51495,27 +51494,22 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R260" t="n">
-        <v>0</v>
+        <v>0.01693265755097047</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U260" t="inlineStr">
-        <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
-        </is>
-      </c>
       <c r="AA260" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -51523,70 +51517,70 @@
       </c>
       <c r="AO260" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP260" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ260" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS260" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT260" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU260" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ260" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -51618,12 +51612,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -51648,7 +51642,7 @@
       </c>
       <c r="L261" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M261" t="inlineStr">
@@ -51657,32 +51651,32 @@
         </is>
       </c>
       <c r="N261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U261" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="V261" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
       <c r="W261" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
       <c r="X261" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Paratyphoid</t>
         </is>
       </c>
       <c r="Y261" t="inlineStr">
@@ -51692,7 +51686,7 @@
       </c>
       <c r="Z261" t="inlineStr">
         <is>
-          <t>notification</t>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA261" t="inlineStr">
@@ -51707,7 +51701,7 @@
       </c>
       <c r="AC261" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:SG:national</t>
         </is>
       </c>
       <c r="AD261" t="inlineStr">
@@ -51742,17 +51736,17 @@
       </c>
       <c r="AJ261" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
       <c r="AK261" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
       <c r="AM261" t="inlineStr">
         <is>
-          <t>provisional</t>
+          <t>provisional; raw</t>
         </is>
       </c>
       <c r="AN261" t="b">
@@ -51760,70 +51754,70 @@
       </c>
       <c r="AO261" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP261" t="inlineStr">
         <is>
-          <t>single_series</t>
+          <t>temporal_handoff</t>
         </is>
       </c>
       <c r="AQ261" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS261" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
       <c r="AT261" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU261" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ261" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC261" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -51855,12 +51849,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -51910,6 +51904,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA262" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -51917,70 +51916,70 @@
       </c>
       <c r="AO262" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP262" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ262" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS262" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT262" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU262" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ262" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC262" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -52012,12 +52011,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -52061,22 +52060,22 @@
       </c>
       <c r="U263" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="V263" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="W263" t="inlineStr">
         <is>
-          <t>SRC_SG_CDA_WIDB</t>
+          <t>SRC_JP_NIID</t>
         </is>
       </c>
       <c r="X263" t="inlineStr">
         <is>
-          <t>Paratyphoid</t>
+          <t>Paratyphoid fever</t>
         </is>
       </c>
       <c r="Y263" t="inlineStr">
@@ -52086,7 +52085,7 @@
       </c>
       <c r="Z263" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_surveillance</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA263" t="inlineStr">
@@ -52101,7 +52100,7 @@
       </c>
       <c r="AC263" t="inlineStr">
         <is>
-          <t>country:SG:national</t>
+          <t>country:JP:national</t>
         </is>
       </c>
       <c r="AD263" t="inlineStr">
@@ -52136,17 +52135,17 @@
       </c>
       <c r="AJ263" t="inlineStr">
         <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
+          <t>JP_NIID_current</t>
         </is>
       </c>
       <c r="AK263" t="inlineStr">
         <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+          <t>Japan NIID paratyphoid-only notifications.</t>
         </is>
       </c>
       <c r="AM263" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>provisional</t>
         </is>
       </c>
       <c r="AN263" t="b">
@@ -52154,70 +52153,70 @@
       </c>
       <c r="AO263" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP263" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ263" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS263" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT263" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU263" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ263" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC263" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -52249,12 +52248,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -52279,7 +52278,7 @@
       </c>
       <c r="L264" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M264" t="inlineStr">
@@ -52288,98 +52287,93 @@
         </is>
       </c>
       <c r="N264" t="n">
+        <v>0</v>
+      </c>
+      <c r="O264" t="n">
+        <v>0</v>
+      </c>
+      <c r="P264" t="n">
+        <v>0</v>
+      </c>
+      <c r="R264" t="n">
+        <v>0</v>
+      </c>
+      <c r="S264" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO264" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP264" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ264" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS264" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT264" t="n">
         <v>2</v>
       </c>
-      <c r="O264" t="n">
-        <v>2</v>
-      </c>
-      <c r="P264" t="n">
-        <v>2</v>
-      </c>
-      <c r="R264" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S264" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U264" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AA264" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO264" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP264" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ264" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS264" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT264" t="n">
-        <v>1</v>
-      </c>
       <c r="AU264" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV264" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY264" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ264" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC264" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -52411,12 +52405,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -52441,7 +52435,7 @@
       </c>
       <c r="L265" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M265" t="inlineStr">
@@ -52450,173 +52444,173 @@
         </is>
       </c>
       <c r="N265" t="n">
+        <v>0</v>
+      </c>
+      <c r="O265" t="n">
+        <v>0</v>
+      </c>
+      <c r="P265" t="n">
+        <v>0</v>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X265" t="inlineStr">
+        <is>
+          <t>Paratyphoid</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB265" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC265" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD265" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE265" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF265" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG265" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH265" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI265" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ265" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK265" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM265" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN265" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO265" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP265" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ265" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS265" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT265" t="n">
         <v>2</v>
       </c>
-      <c r="O265" t="n">
-        <v>2</v>
-      </c>
-      <c r="P265" t="n">
-        <v>2</v>
-      </c>
-      <c r="U265" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="V265" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="W265" t="inlineStr">
-        <is>
-          <t>SRC_US_NNDSS</t>
-        </is>
-      </c>
-      <c r="X265" t="inlineStr">
-        <is>
-          <t>Salmonella Paratyphi infection</t>
-        </is>
-      </c>
-      <c r="Y265" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z265" t="inlineStr">
-        <is>
-          <t>notification</t>
-        </is>
-      </c>
-      <c r="AA265" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AB265" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC265" t="inlineStr">
-        <is>
-          <t>country:US:national</t>
-        </is>
-      </c>
-      <c r="AD265" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE265" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF265" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG265" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH265" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI265" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ265" t="inlineStr">
-        <is>
-          <t>US_NNDSS_Paratyphi_current</t>
-        </is>
-      </c>
-      <c r="AK265" t="inlineStr">
-        <is>
-          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
-        </is>
-      </c>
-      <c r="AM265" t="inlineStr">
-        <is>
-          <t>provisional</t>
-        </is>
-      </c>
-      <c r="AN265" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO265" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP265" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ265" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS265" t="inlineStr">
-        <is>
-          <t>SER_US_PARATYPHI_WEEKLY</t>
-        </is>
-      </c>
-      <c r="AT265" t="n">
-        <v>1</v>
-      </c>
       <c r="AU265" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -52648,12 +52642,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -52678,7 +52672,7 @@
       </c>
       <c r="L266" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M266" t="inlineStr">
@@ -52687,16 +52681,16 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P266" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
@@ -52705,7 +52699,7 @@
       </c>
       <c r="U266" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AA266" t="inlineStr">
@@ -52715,7 +52709,7 @@
       </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
@@ -52725,12 +52719,12 @@
       </c>
       <c r="AQ266" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS266" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT266" t="n">
@@ -52738,47 +52732,47 @@
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -52810,12 +52804,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -52840,7 +52834,7 @@
       </c>
       <c r="L267" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M267" t="inlineStr">
@@ -52849,32 +52843,32 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P267" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U267" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="V267" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="W267" t="inlineStr">
         <is>
-          <t>SRC_JP_NIID</t>
+          <t>SRC_US_NNDSS</t>
         </is>
       </c>
       <c r="X267" t="inlineStr">
         <is>
-          <t>Paratyphoid fever</t>
+          <t>Salmonella Paratyphi infection</t>
         </is>
       </c>
       <c r="Y267" t="inlineStr">
@@ -52899,7 +52893,7 @@
       </c>
       <c r="AC267" t="inlineStr">
         <is>
-          <t>country:JP:national</t>
+          <t>country:US:national</t>
         </is>
       </c>
       <c r="AD267" t="inlineStr">
@@ -52934,12 +52928,12 @@
       </c>
       <c r="AJ267" t="inlineStr">
         <is>
-          <t>JP_NIID_current</t>
+          <t>US_NNDSS_Paratyphi_current</t>
         </is>
       </c>
       <c r="AK267" t="inlineStr">
         <is>
-          <t>Japan NIID paratyphoid-only notifications.</t>
+          <t>United States NNDSS Salmonella Paratyphi infection series; excludes Salmonella Typhi infection.</t>
         </is>
       </c>
       <c r="AM267" t="inlineStr">
@@ -52952,7 +52946,7 @@
       </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>mixed</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
@@ -52962,12 +52956,12 @@
       </c>
       <c r="AQ267" t="inlineStr">
         <is>
-          <t>legacy_gap_fill</t>
+          <t>parity</t>
         </is>
       </c>
       <c r="AS267" t="inlineStr">
         <is>
-          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+          <t>SER_US_PARATYPHI_WEEKLY</t>
         </is>
       </c>
       <c r="AT267" t="n">
@@ -52975,47 +52969,47 @@
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -53047,12 +53041,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -53086,22 +53080,27 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R268" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
       <c r="AA268" t="inlineStr">
         <is>
           <t>weekly</t>
@@ -53109,70 +53108,70 @@
       </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ268" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS268" t="inlineStr">
         <is>
-          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
         </is>
       </c>
       <c r="AT268" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -53204,210 +53203,604 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M269" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N269" t="n">
+        <v>0</v>
+      </c>
+      <c r="O269" t="n">
+        <v>0</v>
+      </c>
+      <c r="P269" t="n">
+        <v>0</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_JP_NIID</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>notification</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:JP:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>JP_NIID_current</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Japan NIID paratyphoid-only notifications.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO269" t="inlineStr">
+        <is>
+          <t>mixed</t>
+        </is>
+      </c>
+      <c r="AP269" t="inlineStr">
+        <is>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_JP_PARATYPHOID_WEEKLY</t>
+        </is>
+      </c>
+      <c r="AT269" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU269" t="inlineStr">
+        <is>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
+        </is>
+      </c>
+      <c r="AV269" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ269" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA269" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB269" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC269" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
           <t>SG</t>
         </is>
       </c>
-      <c r="G269" t="inlineStr">
+      <c r="G270" t="inlineStr">
         <is>
           <t>Singapore</t>
         </is>
       </c>
-      <c r="H269" t="inlineStr">
+      <c r="H270" t="inlineStr">
         <is>
           <t>D234</t>
         </is>
       </c>
-      <c r="I269" t="inlineStr">
-        <is>
-          <t>Paratyphoid fever</t>
-        </is>
-      </c>
-      <c r="J269" t="inlineStr">
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
         <is>
           <t>副伤寒</t>
         </is>
       </c>
-      <c r="K269" t="inlineStr">
+      <c r="K270" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
+      <c r="L270" t="inlineStr">
         <is>
           <t>2026-08-16</t>
         </is>
       </c>
-      <c r="M269" t="inlineStr">
+      <c r="M270" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="N269" t="n">
-        <v>1</v>
-      </c>
-      <c r="O269" t="n">
-        <v>1</v>
-      </c>
-      <c r="P269" t="n">
-        <v>1</v>
-      </c>
-      <c r="U269" t="inlineStr">
+      <c r="N270" t="n">
+        <v>1</v>
+      </c>
+      <c r="O270" t="n">
+        <v>1</v>
+      </c>
+      <c r="P270" t="n">
+        <v>1</v>
+      </c>
+      <c r="R270" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO270" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP270" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
+        </is>
+      </c>
+      <c r="AT270" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU270" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV270" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ270" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA270" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB270" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC270" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>paratyphoid-fever</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>D234</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>Paratyphoid fever</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>副伤寒</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M271" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N271" t="n">
+        <v>1</v>
+      </c>
+      <c r="O271" t="n">
+        <v>1</v>
+      </c>
+      <c r="P271" t="n">
+        <v>1</v>
+      </c>
+      <c r="U271" t="inlineStr">
         <is>
           <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
-      <c r="V269" t="inlineStr">
+      <c r="V271" t="inlineStr">
         <is>
           <t>SER_SG_CDA_PARATYPHOID</t>
         </is>
       </c>
-      <c r="W269" t="inlineStr">
+      <c r="W271" t="inlineStr">
         <is>
           <t>SRC_SG_CDA_WIDB</t>
         </is>
       </c>
-      <c r="X269" t="inlineStr">
+      <c r="X271" t="inlineStr">
         <is>
           <t>Paratyphoid</t>
         </is>
       </c>
-      <c r="Y269" t="inlineStr">
+      <c r="Y271" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z269" t="inlineStr">
+      <c r="Z271" t="inlineStr">
         <is>
           <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
-      <c r="AA269" t="inlineStr">
+      <c r="AA271" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
       </c>
-      <c r="AB269" t="inlineStr">
+      <c r="AB271" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC269" t="inlineStr">
+      <c r="AC271" t="inlineStr">
         <is>
           <t>country:SG:national</t>
         </is>
       </c>
-      <c r="AD269" t="inlineStr">
+      <c r="AD271" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE269" t="inlineStr">
+      <c r="AE271" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF269" t="inlineStr">
+      <c r="AF271" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG269" t="inlineStr">
+      <c r="AG271" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH269" t="inlineStr">
+      <c r="AH271" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI269" t="inlineStr">
+      <c r="AI271" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ269" t="inlineStr">
+      <c r="AJ271" t="inlineStr">
         <is>
           <t>SG_CDA_WIDB_2023_CURRENT</t>
         </is>
       </c>
-      <c r="AK269" t="inlineStr">
+      <c r="AK271" t="inlineStr">
         <is>
           <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
         </is>
       </c>
-      <c r="AM269" t="inlineStr">
+      <c r="AM271" t="inlineStr">
         <is>
           <t>provisional; raw</t>
         </is>
       </c>
-      <c r="AN269" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO269" t="inlineStr">
+      <c r="AN271" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO271" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP269" t="inlineStr">
+      <c r="AP271" t="inlineStr">
         <is>
           <t>temporal_handoff</t>
         </is>
       </c>
-      <c r="AQ269" t="inlineStr">
+      <c r="AQ271" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AS269" t="inlineStr">
+      <c r="AS271" t="inlineStr">
         <is>
           <t>SER_SG_CDA_PARATYPHOID; SER_SG_HIST_PARATYPHOID</t>
         </is>
       </c>
-      <c r="AT269" t="n">
+      <c r="AT271" t="n">
         <v>2</v>
       </c>
-      <c r="AU269" t="inlineStr">
+      <c r="AU271" t="inlineStr">
         <is>
           <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
-      <c r="AV269" t="inlineStr">
+      <c r="AV271" t="inlineStr">
         <is>
           <t>cda_weekly_bulletin</t>
         </is>
       </c>
-      <c r="AW269" t="inlineStr">
+      <c r="AW271" t="inlineStr">
         <is>
           <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
-      <c r="AX269" t="inlineStr">
+      <c r="AX271" t="inlineStr">
         <is>
           <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
-      <c r="AY269" t="inlineStr">
+      <c r="AY271" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
       </c>
-      <c r="AZ269" t="inlineStr">
+      <c r="AZ271" t="inlineStr">
         <is>
           <t>cda_weekly_bulletin</t>
         </is>
       </c>
-      <c r="BA269" t="inlineStr">
+      <c r="BA271" t="inlineStr">
         <is>
           <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
-      <c r="BB269" t="inlineStr">
+      <c r="BB271" t="inlineStr">
         <is>
           <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
-      <c r="BC269" t="inlineStr">
+      <c r="BC271" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -53529,7 +53922,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -53539,7 +53932,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11">
@@ -53559,7 +53952,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13">
@@ -53591,7 +53984,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16">
